--- a/Project_API_Documentation.xlsx
+++ b/Project_API_Documentation.xlsx
@@ -9,6 +9,13 @@
     <sheet name="Customer" sheetId="4" r:id="rId4"/>
     <sheet name="Hotel Partner" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Auth &amp; Public'!A1:I14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Admin Dashboard'!A1:I47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Tour Operator'!A1:I32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3">'Customer'!A1:I23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Hotel Partner'!A1:I29</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -401,35 +408,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I14"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="46.83203125" customWidth="1"/>
+    <col min="7" max="7" width="46.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" customWidth="1"/>
+    <col min="9" max="9" width="52.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>S.No</v>
       </c>
       <c r="B1" t="str">
-        <v>Type of Dashboard</v>
+        <v>Dashboard Type</v>
       </c>
       <c r="C1" t="str">
-        <v>HTTP Method</v>
+        <v>API Endpoint</v>
       </c>
       <c r="D1" t="str">
-        <v>API Path</v>
+        <v>Method</v>
       </c>
       <c r="E1" t="str">
-        <v>Description</v>
+        <v>Auth</v>
       </c>
       <c r="F1" t="str">
-        <v>Sample Request Body (JSON)</v>
+        <v>Request Body</v>
       </c>
       <c r="G1" t="str">
-        <v>Sample Response (JSON)</v>
+        <v>Sample Response</v>
       </c>
       <c r="H1" t="str">
-        <v>Success Status Code</v>
+        <v>Status Codes</v>
       </c>
       <c r="I1" t="str">
-        <v>Error Status Codes</v>
+        <v>Notes</v>
       </c>
     </row>
     <row r="2">
@@ -440,13 +458,13 @@
         <v>Auth/Public</v>
       </c>
       <c r="C2" t="str">
+        <v>/api/signup</v>
+      </c>
+      <c r="D2" t="str">
         <v>POST</v>
       </c>
-      <c r="D2" t="str">
-        <v>/api/signup</v>
-      </c>
       <c r="E2" t="str">
-        <v>Register a new user</v>
+        <v>None (public)</v>
       </c>
       <c r="F2" t="str">
         <v>{ "fullName": "John Doe", "email": "john@test.com", "phone": "8000000001", "password": "Pass123", "role": "customer" }</v>
@@ -454,11 +472,11 @@
       <c r="G2" t="str">
         <v>{ "message": "User registered successfully", "userId": "6abc123..." }</v>
       </c>
-      <c r="H2">
-        <v>201</v>
+      <c r="H2" t="str">
+        <v>201 on success; 400/409 on error</v>
       </c>
       <c r="I2" t="str">
-        <v>400/409</v>
+        <v>Register a new user</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +487,13 @@
         <v>Auth/Public</v>
       </c>
       <c r="C3" t="str">
+        <v>/api/login</v>
+      </c>
+      <c r="D3" t="str">
         <v>POST</v>
       </c>
-      <c r="D3" t="str">
-        <v>/api/login</v>
-      </c>
       <c r="E3" t="str">
-        <v>Login and get JWT token</v>
+        <v>None (public)</v>
       </c>
       <c r="F3" t="str">
         <v>{ "email": "john@test.com", "password": "Pass123", "role": "customer" }</v>
@@ -483,11 +501,11 @@
       <c r="G3" t="str">
         <v>{ "message": "Login successful", "token": "eyJhbG..." }</v>
       </c>
-      <c r="H3">
-        <v>200</v>
+      <c r="H3" t="str">
+        <v>200 on success; 401/403 on error</v>
       </c>
       <c r="I3" t="str">
-        <v>401/403</v>
+        <v>Login and get JWT token</v>
       </c>
     </row>
     <row r="4">
@@ -498,13 +516,13 @@
         <v>Auth/Public</v>
       </c>
       <c r="C4" t="str">
+        <v>/api/forgot-password</v>
+      </c>
+      <c r="D4" t="str">
         <v>POST</v>
       </c>
-      <c r="D4" t="str">
-        <v>/api/forgot-password</v>
-      </c>
       <c r="E4" t="str">
-        <v>Request password reset OTP</v>
+        <v>None (public)</v>
       </c>
       <c r="F4" t="str">
         <v>{ "email": "john@test.com" }</v>
@@ -512,11 +530,11 @@
       <c r="G4" t="str">
         <v>{ "message": "OTP sent to your email" }</v>
       </c>
-      <c r="H4">
-        <v>200</v>
+      <c r="H4" t="str">
+        <v>200 on success; 404 on error</v>
       </c>
       <c r="I4" t="str">
-        <v>404</v>
+        <v>Request password reset OTP</v>
       </c>
     </row>
     <row r="5">
@@ -527,13 +545,13 @@
         <v>Auth/Public</v>
       </c>
       <c r="C5" t="str">
+        <v>/api/verify-otp</v>
+      </c>
+      <c r="D5" t="str">
         <v>POST</v>
       </c>
-      <c r="D5" t="str">
-        <v>/api/verify-otp</v>
-      </c>
       <c r="E5" t="str">
-        <v>Verify OTP for password reset</v>
+        <v>None (public)</v>
       </c>
       <c r="F5" t="str">
         <v>{ "email": "john@test.com", "otp": "123456" }</v>
@@ -541,11 +559,11 @@
       <c r="G5" t="str">
         <v>{ "message": "OTP verified successfully" }</v>
       </c>
-      <c r="H5">
-        <v>200</v>
+      <c r="H5" t="str">
+        <v>200 on success; 400 on error</v>
       </c>
       <c r="I5" t="str">
-        <v>400</v>
+        <v>Verify OTP for password reset</v>
       </c>
     </row>
     <row r="6">
@@ -556,13 +574,13 @@
         <v>Auth/Public</v>
       </c>
       <c r="C6" t="str">
+        <v>/api/reset-password</v>
+      </c>
+      <c r="D6" t="str">
         <v>POST</v>
       </c>
-      <c r="D6" t="str">
-        <v>/api/reset-password</v>
-      </c>
       <c r="E6" t="str">
-        <v>Reset password using valid OTP</v>
+        <v>None (public)</v>
       </c>
       <c r="F6" t="str">
         <v>{ "email": "john@test.com", "otp": "123456", "newPassword": "NewPass@123" }</v>
@@ -570,11 +588,11 @@
       <c r="G6" t="str">
         <v>{ "message": "Password reset successfully" }</v>
       </c>
-      <c r="H6">
-        <v>200</v>
+      <c r="H6" t="str">
+        <v>200 on success; 400/404/500 on error</v>
       </c>
       <c r="I6" t="str">
-        <v>400/404/500</v>
+        <v>Reset password using valid OTP</v>
       </c>
     </row>
     <row r="7">
@@ -585,13 +603,13 @@
         <v>Public</v>
       </c>
       <c r="C7" t="str">
-        <v>GET</v>
+        <v>/api/packages</v>
       </c>
       <c r="D7" t="str">
-        <v>/api/packages</v>
+        <v>GET</v>
       </c>
       <c r="E7" t="str">
-        <v>List all published packages</v>
+        <v>None (public)</v>
       </c>
       <c r="F7" t="str">
         <v>?publishedOnly=true</v>
@@ -599,11 +617,11 @@
       <c r="G7" t="str">
         <v>{ "packages": [{ "_id": "..." }] }</v>
       </c>
-      <c r="H7">
-        <v>200</v>
+      <c r="H7" t="str">
+        <v>200 on success; 500 on error</v>
       </c>
       <c r="I7" t="str">
-        <v>500</v>
+        <v>List all published packages. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="8">
@@ -614,13 +632,13 @@
         <v>Public</v>
       </c>
       <c r="C8" t="str">
-        <v>GET</v>
+        <v>/api/packages/:id</v>
       </c>
       <c r="D8" t="str">
-        <v>/api/packages/:id</v>
+        <v>GET</v>
       </c>
       <c r="E8" t="str">
-        <v>Get a single package</v>
+        <v>None (public)</v>
       </c>
       <c r="F8" t="str">
         <v>/{packageId}</v>
@@ -628,11 +646,11 @@
       <c r="G8" t="str">
         <v>{ "package": { "_id": "..." } }</v>
       </c>
-      <c r="H8">
-        <v>200</v>
+      <c r="H8" t="str">
+        <v>200 on success; 404/500 on error</v>
       </c>
       <c r="I8" t="str">
-        <v>404/500</v>
+        <v>Get a single package</v>
       </c>
     </row>
     <row r="9">
@@ -643,13 +661,13 @@
         <v>Public</v>
       </c>
       <c r="C9" t="str">
-        <v>GET</v>
+        <v>/api/public/hotels</v>
       </c>
       <c r="D9" t="str">
-        <v>/api/public/hotels</v>
+        <v>GET</v>
       </c>
       <c r="E9" t="str">
-        <v>List all hotels (public)</v>
+        <v>None (public)</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -657,11 +675,11 @@
       <c r="G9" t="str">
         <v>{ "hotels": [...] }</v>
       </c>
-      <c r="H9">
-        <v>200</v>
+      <c r="H9" t="str">
+        <v>200 on success; 500 on error</v>
       </c>
       <c r="I9" t="str">
-        <v>500</v>
+        <v>List all hotels (public). Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="10">
@@ -672,13 +690,13 @@
         <v>Public</v>
       </c>
       <c r="C10" t="str">
-        <v>GET</v>
+        <v>/api/public/hotels/:id</v>
       </c>
       <c r="D10" t="str">
-        <v>/api/public/hotels/:id</v>
+        <v>GET</v>
       </c>
       <c r="E10" t="str">
-        <v>Get hotel details (public)</v>
+        <v>None (public)</v>
       </c>
       <c r="F10" t="str">
         <v>/{hotelId}</v>
@@ -686,11 +704,11 @@
       <c r="G10" t="str">
         <v>{ "hotel": { "name": "Grand Hotel" } }</v>
       </c>
-      <c r="H10">
-        <v>200</v>
+      <c r="H10" t="str">
+        <v>200 on success; 404/500 on error</v>
       </c>
       <c r="I10" t="str">
-        <v>404/500</v>
+        <v>Get hotel details (public)</v>
       </c>
     </row>
     <row r="11">
@@ -701,13 +719,13 @@
         <v>Public</v>
       </c>
       <c r="C11" t="str">
-        <v>GET</v>
+        <v>/api/public/destinations</v>
       </c>
       <c r="D11" t="str">
-        <v>/api/public/destinations</v>
+        <v>GET</v>
       </c>
       <c r="E11" t="str">
-        <v>List all destinations (public)</v>
+        <v>None (public)</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -715,51 +733,150 @@
       <c r="G11" t="str">
         <v>{ "destinations": [...] }</v>
       </c>
-      <c r="H11">
-        <v>200</v>
+      <c r="H11" t="str">
+        <v>200 on success; 500 on error</v>
       </c>
       <c r="I11" t="str">
-        <v>500</v>
+        <v>List all destinations (public). Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>137</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Auth/Public</v>
+      </c>
+      <c r="C12" t="str">
+        <v>/api/auth/google</v>
+      </c>
+      <c r="D12" t="str">
+        <v>GET</v>
+      </c>
+      <c r="E12" t="str">
+        <v>None (public)</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v>Redirects to accounts.google.com with an OAuth state parameter</v>
+      </c>
+      <c r="H12" t="str">
+        <v>302 on success; 500 on error</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Start Google OAuth sign-in</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>138</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Auth/Public</v>
+      </c>
+      <c r="C13" t="str">
+        <v>/api/auth/google/callback</v>
+      </c>
+      <c r="D13" t="str">
+        <v>GET</v>
+      </c>
+      <c r="E13" t="str">
+        <v>None (public)</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v>{ "token": "eyJhbG...", "user": { "role": "customer" } }</v>
+      </c>
+      <c r="H13" t="str">
+        <v>200 on success; 401/500 on error</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Google OAuth callback, issues a session token</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>139</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Public</v>
+      </c>
+      <c r="C14" t="str">
+        <v>/api/contact</v>
+      </c>
+      <c r="D14" t="str">
+        <v>POST</v>
+      </c>
+      <c r="E14" t="str">
+        <v>None (public)</v>
+      </c>
+      <c r="F14" t="str">
+        <v>{ "fullName": "John Doe", "email": "john@test.com", "phone": "8000000001", "subject": " enquiry", "message": "Enquiry about Manali packages" }</v>
+      </c>
+      <c r="G14" t="str">
+        <v>{ "message": "Message sent successfully" }</v>
+      </c>
+      <c r="H14" t="str">
+        <v>201 on success; 400/500 on error</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Submit a public contact form message</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I14"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:I47"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="46.83203125" customWidth="1"/>
+    <col min="7" max="7" width="46.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" customWidth="1"/>
+    <col min="9" max="9" width="52.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>S.No</v>
       </c>
       <c r="B1" t="str">
-        <v>Type of Dashboard</v>
+        <v>Dashboard Type</v>
       </c>
       <c r="C1" t="str">
-        <v>HTTP Method</v>
+        <v>API Endpoint</v>
       </c>
       <c r="D1" t="str">
-        <v>API Path</v>
+        <v>Method</v>
       </c>
       <c r="E1" t="str">
-        <v>Description</v>
+        <v>Auth</v>
       </c>
       <c r="F1" t="str">
-        <v>Sample Request Body (JSON)</v>
+        <v>Request Body</v>
       </c>
       <c r="G1" t="str">
-        <v>Sample Response (JSON)</v>
+        <v>Sample Response</v>
       </c>
       <c r="H1" t="str">
-        <v>Success Status Code</v>
+        <v>Status Codes</v>
       </c>
       <c r="I1" t="str">
-        <v>Error Status Codes</v>
+        <v>Notes</v>
       </c>
     </row>
     <row r="2">
@@ -770,13 +887,13 @@
         <v>Admin</v>
       </c>
       <c r="C2" t="str">
-        <v>GET</v>
+        <v>/api/admin/users</v>
       </c>
       <c r="D2" t="str">
-        <v>/api/admin/users</v>
+        <v>GET</v>
       </c>
       <c r="E2" t="str">
-        <v>List all users</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -784,11 +901,11 @@
       <c r="G2" t="str">
         <v>{ "users": [{ "id": "..." }] }</v>
       </c>
-      <c r="H2">
-        <v>200</v>
+      <c r="H2" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I2" t="str">
-        <v>401/403/500</v>
+        <v>List all users. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="3">
@@ -799,13 +916,13 @@
         <v>Admin</v>
       </c>
       <c r="C3" t="str">
+        <v>/api/admin/users</v>
+      </c>
+      <c r="D3" t="str">
         <v>POST</v>
       </c>
-      <c r="D3" t="str">
-        <v>/api/admin/users</v>
-      </c>
       <c r="E3" t="str">
-        <v>Create new user</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F3" t="str">
         <v>{ "fullName": "Jane Admin", "email": "jane@test.com", "phone": "8000000002", "password": "Pass123", "role": "tour_operator" }</v>
@@ -813,11 +930,11 @@
       <c r="G3" t="str">
         <v>{ "message": "User created successfully" }</v>
       </c>
-      <c r="H3">
-        <v>201</v>
+      <c r="H3" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I3" t="str">
-        <v>400/401/403/500</v>
+        <v>Create new user</v>
       </c>
     </row>
     <row r="4">
@@ -828,28 +945,25 @@
         <v>Admin</v>
       </c>
       <c r="C4" t="str">
+        <v>/api/admin/users/:id</v>
+      </c>
+      <c r="D4" t="str">
         <v>PUT</v>
       </c>
-      <c r="D4" t="str">
-        <v>/api/admin/users/:id</v>
-      </c>
       <c r="E4" t="str">
-        <v>Update user</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F4" t="str">
-        <v>/{userId}</v>
+        <v>{ "fullName": "Jane", "phone": "8000000099" }</v>
       </c>
       <c r="G4" t="str">
-        <v>{ "fullName": "Jane", "phone": "8000000099" }</v>
+        <v>{ "message": "User updated successfully" }</v>
       </c>
       <c r="H4" t="str">
-        <v>{ "message": "User updated successfully" }</v>
-      </c>
-      <c r="I4">
-        <v>200</v>
-      </c>
-      <c r="J4" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Update user. Path params: {userId}</v>
       </c>
     </row>
     <row r="5">
@@ -860,28 +974,25 @@
         <v>Admin</v>
       </c>
       <c r="C5" t="str">
+        <v>/api/admin/users/:id</v>
+      </c>
+      <c r="D5" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D5" t="str">
-        <v>/api/admin/users/:id</v>
-      </c>
       <c r="E5" t="str">
-        <v>Delete user</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F5" t="str">
-        <v>/{userId}</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>{ "message": "User deleted successfully" }</v>
       </c>
       <c r="H5" t="str">
-        <v>{ "message": "User deleted successfully" }</v>
-      </c>
-      <c r="I5">
-        <v>200</v>
-      </c>
-      <c r="J5" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Delete user. Path params: {userId}</v>
       </c>
     </row>
     <row r="6">
@@ -892,13 +1003,13 @@
         <v>Admin</v>
       </c>
       <c r="C6" t="str">
-        <v>GET</v>
+        <v>/api/admin/packages</v>
       </c>
       <c r="D6" t="str">
-        <v>/api/admin/packages</v>
+        <v>GET</v>
       </c>
       <c r="E6" t="str">
-        <v>List all packages</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -906,11 +1017,11 @@
       <c r="G6" t="str">
         <v>{ "packages": [{ "_id": "..." }] }</v>
       </c>
-      <c r="H6">
-        <v>200</v>
+      <c r="H6" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I6" t="str">
-        <v>401/403/500</v>
+        <v>List all packages. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="7">
@@ -921,13 +1032,13 @@
         <v>Admin</v>
       </c>
       <c r="C7" t="str">
+        <v>/api/admin/packages</v>
+      </c>
+      <c r="D7" t="str">
         <v>POST</v>
       </c>
-      <c r="D7" t="str">
-        <v>/api/admin/packages</v>
-      </c>
       <c r="E7" t="str">
-        <v>Create new package</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F7" t="str">
         <v>{ "name": "Manali Trip", "destination": "Manali", "duration": "4 Days", "price": 12000, "rating": 4, "status": "active", "publishedStatus": "published", "description": "Adventure trip", "inclusions": ["Stay"], "image": "https://via.placeholder.com/400x300", "category": "Adventure", "shortDescription": "Short desc" }</v>
@@ -935,11 +1046,11 @@
       <c r="G7" t="str">
         <v>{ "message": "Package created successfully" }</v>
       </c>
-      <c r="H7">
-        <v>201</v>
+      <c r="H7" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I7" t="str">
-        <v>400/401/403/500</v>
+        <v>Create new package</v>
       </c>
     </row>
     <row r="8">
@@ -950,28 +1061,25 @@
         <v>Admin</v>
       </c>
       <c r="C8" t="str">
+        <v>/api/admin/packages/:id</v>
+      </c>
+      <c r="D8" t="str">
         <v>PUT</v>
       </c>
-      <c r="D8" t="str">
-        <v>/api/admin/packages/:id</v>
-      </c>
       <c r="E8" t="str">
-        <v>Update package</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F8" t="str">
-        <v>/{packageId}</v>
+        <v>{ "price": 15000, "status": "inactive" }</v>
       </c>
       <c r="G8" t="str">
-        <v>{ "price": 15000, "status": "inactive" }</v>
+        <v>{ "message": "Package updated successfully" }</v>
       </c>
       <c r="H8" t="str">
-        <v>{ "message": "Package updated successfully" }</v>
-      </c>
-      <c r="I8">
-        <v>200</v>
-      </c>
-      <c r="J8" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Update package. Path params: {packageId}</v>
       </c>
     </row>
     <row r="9">
@@ -982,28 +1090,25 @@
         <v>Admin</v>
       </c>
       <c r="C9" t="str">
+        <v>/api/admin/packages/:id</v>
+      </c>
+      <c r="D9" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D9" t="str">
-        <v>/api/admin/packages/:id</v>
-      </c>
       <c r="E9" t="str">
-        <v>Delete package</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F9" t="str">
-        <v>/{packageId}</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>{ "message": "Package deleted successfully" }</v>
       </c>
       <c r="H9" t="str">
-        <v>{ "message": "Package deleted successfully" }</v>
-      </c>
-      <c r="I9">
-        <v>200</v>
-      </c>
-      <c r="J9" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Delete package. Path params: {packageId}</v>
       </c>
     </row>
     <row r="10">
@@ -1014,13 +1119,13 @@
         <v>Admin</v>
       </c>
       <c r="C10" t="str">
-        <v>GET</v>
+        <v>/api/admin/itineraries</v>
       </c>
       <c r="D10" t="str">
-        <v>/api/admin/itineraries</v>
+        <v>GET</v>
       </c>
       <c r="E10" t="str">
-        <v>List all itineraries</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -1028,11 +1133,11 @@
       <c r="G10" t="str">
         <v>{ "itineraries": [...] }</v>
       </c>
-      <c r="H10">
-        <v>200</v>
+      <c r="H10" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I10" t="str">
-        <v>401/403/500</v>
+        <v>List all itineraries. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="11">
@@ -1043,13 +1148,13 @@
         <v>Admin</v>
       </c>
       <c r="C11" t="str">
+        <v>/api/admin/itineraries</v>
+      </c>
+      <c r="D11" t="str">
         <v>POST</v>
       </c>
-      <c r="D11" t="str">
-        <v>/api/admin/itineraries</v>
-      </c>
       <c r="E11" t="str">
-        <v>Create itinerary</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F11" t="str">
         <v>{ "name": "Day 1", "packageId": "&lt;pkgId&gt;", "packageName": "Manali Trip", "days": 4, "hotels": ["Hotel A"], "status": "active" }</v>
@@ -1057,11 +1162,11 @@
       <c r="G11" t="str">
         <v>{ "message": "Itinerary created successfully" }</v>
       </c>
-      <c r="H11">
-        <v>201</v>
+      <c r="H11" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I11" t="str">
-        <v>400/401/403/500</v>
+        <v>Create itinerary</v>
       </c>
     </row>
     <row r="12">
@@ -1072,28 +1177,25 @@
         <v>Admin</v>
       </c>
       <c r="C12" t="str">
+        <v>/api/admin/itineraries/:id</v>
+      </c>
+      <c r="D12" t="str">
         <v>PUT</v>
       </c>
-      <c r="D12" t="str">
-        <v>/api/admin/itineraries/:id</v>
-      </c>
       <c r="E12" t="str">
-        <v>Update itinerary</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F12" t="str">
-        <v>/{id}</v>
+        <v>{ "name": "Updated", "status": "active" }</v>
       </c>
       <c r="G12" t="str">
-        <v>{ "name": "Updated", "status": "active" }</v>
+        <v>{ "message": "Itinerary updated successfully" }</v>
       </c>
       <c r="H12" t="str">
-        <v>{ "message": "Itinerary updated successfully" }</v>
-      </c>
-      <c r="I12">
-        <v>200</v>
-      </c>
-      <c r="J12" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Update itinerary. Path params: {id}</v>
       </c>
     </row>
     <row r="13">
@@ -1104,28 +1206,25 @@
         <v>Admin</v>
       </c>
       <c r="C13" t="str">
+        <v>/api/admin/itineraries/:id</v>
+      </c>
+      <c r="D13" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D13" t="str">
-        <v>/api/admin/itineraries/:id</v>
-      </c>
       <c r="E13" t="str">
-        <v>Delete itinerary</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F13" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>{ "message": "Itinerary deleted successfully" }</v>
       </c>
       <c r="H13" t="str">
-        <v>{ "message": "Itinerary deleted successfully" }</v>
-      </c>
-      <c r="I13">
-        <v>200</v>
-      </c>
-      <c r="J13" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Delete itinerary. Path params: {id}</v>
       </c>
     </row>
     <row r="14">
@@ -1136,13 +1235,13 @@
         <v>Admin</v>
       </c>
       <c r="C14" t="str">
-        <v>GET</v>
+        <v>/api/admin/hotels</v>
       </c>
       <c r="D14" t="str">
-        <v>/api/admin/hotels</v>
+        <v>GET</v>
       </c>
       <c r="E14" t="str">
-        <v>List all hotels</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -1150,11 +1249,11 @@
       <c r="G14" t="str">
         <v>{ "hotels": [...] }</v>
       </c>
-      <c r="H14">
-        <v>200</v>
+      <c r="H14" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I14" t="str">
-        <v>401/403/500</v>
+        <v>List all hotels. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="15">
@@ -1165,13 +1264,13 @@
         <v>Admin</v>
       </c>
       <c r="C15" t="str">
+        <v>/api/admin/hotels</v>
+      </c>
+      <c r="D15" t="str">
         <v>POST</v>
       </c>
-      <c r="D15" t="str">
-        <v>/api/admin/hotels</v>
-      </c>
       <c r="E15" t="str">
-        <v>Create hotel</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F15" t="str">
         <v>{ "name": "Grand Palace", "location": "Jaipur", "rooms": 10, "rating": 4 }</v>
@@ -1179,11 +1278,11 @@
       <c r="G15" t="str">
         <v>{ "message": "Hotel created successfully" }</v>
       </c>
-      <c r="H15">
-        <v>201</v>
+      <c r="H15" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I15" t="str">
-        <v>400/401/403/500</v>
+        <v>Create hotel</v>
       </c>
     </row>
     <row r="16">
@@ -1194,28 +1293,25 @@
         <v>Admin</v>
       </c>
       <c r="C16" t="str">
+        <v>/api/admin/hotels/:id</v>
+      </c>
+      <c r="D16" t="str">
         <v>PUT</v>
       </c>
-      <c r="D16" t="str">
-        <v>/api/admin/hotels/:id</v>
-      </c>
       <c r="E16" t="str">
-        <v>Update hotel</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F16" t="str">
-        <v>/{id}</v>
+        <v>{ "name": "Updated" }</v>
       </c>
       <c r="G16" t="str">
-        <v>{ "name": "Updated" }</v>
+        <v>{ "message": "Hotel updated successfully" }</v>
       </c>
       <c r="H16" t="str">
-        <v>{ "message": "Hotel updated successfully" }</v>
-      </c>
-      <c r="I16">
-        <v>200</v>
-      </c>
-      <c r="J16" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Update hotel. Path params: {id}</v>
       </c>
     </row>
     <row r="17">
@@ -1226,28 +1322,25 @@
         <v>Admin</v>
       </c>
       <c r="C17" t="str">
+        <v>/api/admin/hotels/:id</v>
+      </c>
+      <c r="D17" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D17" t="str">
-        <v>/api/admin/hotels/:id</v>
-      </c>
       <c r="E17" t="str">
-        <v>Delete hotel</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F17" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>{ "message": "Hotel deleted successfully" }</v>
       </c>
       <c r="H17" t="str">
-        <v>{ "message": "Hotel deleted successfully" }</v>
-      </c>
-      <c r="I17">
-        <v>200</v>
-      </c>
-      <c r="J17" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Delete hotel. Path params: {id}</v>
       </c>
     </row>
     <row r="18">
@@ -1258,13 +1351,13 @@
         <v>Admin</v>
       </c>
       <c r="C18" t="str">
-        <v>GET</v>
+        <v>/api/admin/rooms</v>
       </c>
       <c r="D18" t="str">
-        <v>/api/admin/rooms</v>
+        <v>GET</v>
       </c>
       <c r="E18" t="str">
-        <v>List all rooms</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -1272,11 +1365,11 @@
       <c r="G18" t="str">
         <v>{ "rooms": [...] }</v>
       </c>
-      <c r="H18">
-        <v>200</v>
+      <c r="H18" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I18" t="str">
-        <v>401/403/500</v>
+        <v>List all rooms. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="19">
@@ -1287,13 +1380,13 @@
         <v>Admin</v>
       </c>
       <c r="C19" t="str">
+        <v>/api/admin/rooms</v>
+      </c>
+      <c r="D19" t="str">
         <v>POST</v>
       </c>
-      <c r="D19" t="str">
-        <v>/api/admin/rooms</v>
-      </c>
       <c r="E19" t="str">
-        <v>Create room</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F19" t="str">
         <v>{ "hotel": "&lt;hotelId&gt;", "type": "Deluxe", "total": 10, "price": 3500 }</v>
@@ -1301,11 +1394,11 @@
       <c r="G19" t="str">
         <v>{ "message": "Room created successfully" }</v>
       </c>
-      <c r="H19">
-        <v>201</v>
+      <c r="H19" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I19" t="str">
-        <v>400/401/403/500</v>
+        <v>Create room</v>
       </c>
     </row>
     <row r="20">
@@ -1316,28 +1409,25 @@
         <v>Admin</v>
       </c>
       <c r="C20" t="str">
+        <v>/api/admin/rooms/:id</v>
+      </c>
+      <c r="D20" t="str">
         <v>PUT</v>
       </c>
-      <c r="D20" t="str">
-        <v>/api/admin/rooms/:id</v>
-      </c>
       <c r="E20" t="str">
-        <v>Update room</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F20" t="str">
-        <v>/{id}</v>
+        <v>{ "price": 4000 }</v>
       </c>
       <c r="G20" t="str">
-        <v>{ "price": 4000 }</v>
+        <v>{ "message": "Room updated successfully" }</v>
       </c>
       <c r="H20" t="str">
-        <v>{ "message": "Room updated successfully" }</v>
-      </c>
-      <c r="I20">
-        <v>200</v>
-      </c>
-      <c r="J20" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Update room. Path params: {id}</v>
       </c>
     </row>
     <row r="21">
@@ -1348,28 +1438,25 @@
         <v>Admin</v>
       </c>
       <c r="C21" t="str">
+        <v>/api/admin/rooms/:id</v>
+      </c>
+      <c r="D21" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D21" t="str">
-        <v>/api/admin/rooms/:id</v>
-      </c>
       <c r="E21" t="str">
-        <v>Delete room</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F21" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>{ "message": "Room deleted successfully" }</v>
       </c>
       <c r="H21" t="str">
-        <v>{ "message": "Room deleted successfully" }</v>
-      </c>
-      <c r="I21">
-        <v>200</v>
-      </c>
-      <c r="J21" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Delete room. Path params: {id}</v>
       </c>
     </row>
     <row r="22">
@@ -1380,13 +1467,13 @@
         <v>Admin</v>
       </c>
       <c r="C22" t="str">
-        <v>GET</v>
+        <v>/api/admin/bookings</v>
       </c>
       <c r="D22" t="str">
-        <v>/api/admin/bookings</v>
+        <v>GET</v>
       </c>
       <c r="E22" t="str">
-        <v>List all bookings</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -1394,11 +1481,11 @@
       <c r="G22" t="str">
         <v>{ "bookings": [...] }</v>
       </c>
-      <c r="H22">
-        <v>200</v>
+      <c r="H22" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I22" t="str">
-        <v>401/403/500</v>
+        <v>List all bookings. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="23">
@@ -1409,13 +1496,13 @@
         <v>Admin</v>
       </c>
       <c r="C23" t="str">
+        <v>/api/admin/bookings</v>
+      </c>
+      <c r="D23" t="str">
         <v>POST</v>
       </c>
-      <c r="D23" t="str">
-        <v>/api/admin/bookings</v>
-      </c>
       <c r="E23" t="str">
-        <v>Create booking</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F23" t="str">
         <v>{ "customer": "&lt;custId&gt;", "email": "cust@test.com", "package": "Trip", "amount": 12000 }</v>
@@ -1423,11 +1510,11 @@
       <c r="G23" t="str">
         <v>{ "message": "Booking created successfully" }</v>
       </c>
-      <c r="H23">
-        <v>201</v>
+      <c r="H23" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I23" t="str">
-        <v>400/401/403/500</v>
+        <v>Create booking</v>
       </c>
     </row>
     <row r="24">
@@ -1438,28 +1525,25 @@
         <v>Admin</v>
       </c>
       <c r="C24" t="str">
+        <v>/api/admin/bookings/:id</v>
+      </c>
+      <c r="D24" t="str">
         <v>PUT</v>
       </c>
-      <c r="D24" t="str">
-        <v>/api/admin/bookings/:id</v>
-      </c>
       <c r="E24" t="str">
-        <v>Update booking</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F24" t="str">
-        <v>/{id}</v>
+        <v>{ "status": "confirmed" }</v>
       </c>
       <c r="G24" t="str">
-        <v>{ "status": "confirmed" }</v>
+        <v>{ "message": "Booking updated successfully" }</v>
       </c>
       <c r="H24" t="str">
-        <v>{ "message": "Booking updated successfully" }</v>
-      </c>
-      <c r="I24">
-        <v>200</v>
-      </c>
-      <c r="J24" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Update booking. Path params: {id}</v>
       </c>
     </row>
     <row r="25">
@@ -1470,28 +1554,25 @@
         <v>Admin</v>
       </c>
       <c r="C25" t="str">
+        <v>/api/admin/bookings/:id</v>
+      </c>
+      <c r="D25" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D25" t="str">
-        <v>/api/admin/bookings/:id</v>
-      </c>
       <c r="E25" t="str">
-        <v>Delete booking</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F25" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>{ "message": "Booking deleted successfully" }</v>
       </c>
       <c r="H25" t="str">
-        <v>{ "message": "Booking deleted successfully" }</v>
-      </c>
-      <c r="I25">
-        <v>200</v>
-      </c>
-      <c r="J25" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Delete booking. Path params: {id}</v>
       </c>
     </row>
     <row r="26">
@@ -1502,13 +1583,13 @@
         <v>Admin</v>
       </c>
       <c r="C26" t="str">
-        <v>GET</v>
+        <v>/api/admin/invoices</v>
       </c>
       <c r="D26" t="str">
-        <v>/api/admin/invoices</v>
+        <v>GET</v>
       </c>
       <c r="E26" t="str">
-        <v>List all invoices</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -1516,11 +1597,11 @@
       <c r="G26" t="str">
         <v>{ "invoices": [...] }</v>
       </c>
-      <c r="H26">
-        <v>200</v>
+      <c r="H26" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I26" t="str">
-        <v>401/403/500</v>
+        <v>List all invoices. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="27">
@@ -1531,13 +1612,13 @@
         <v>Admin</v>
       </c>
       <c r="C27" t="str">
+        <v>/api/admin/invoices</v>
+      </c>
+      <c r="D27" t="str">
         <v>POST</v>
       </c>
-      <c r="D27" t="str">
-        <v>/api/admin/invoices</v>
-      </c>
       <c r="E27" t="str">
-        <v>Create invoice</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F27" t="str">
         <v>{ "invoiceNo": "INV001", "customer": "&lt;custId&gt;", "amount": 12000 }</v>
@@ -1545,11 +1626,11 @@
       <c r="G27" t="str">
         <v>{ "message": "Invoice created successfully" }</v>
       </c>
-      <c r="H27">
-        <v>201</v>
+      <c r="H27" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I27" t="str">
-        <v>400/401/403/500</v>
+        <v>Create invoice</v>
       </c>
     </row>
     <row r="28">
@@ -1560,28 +1641,25 @@
         <v>Admin</v>
       </c>
       <c r="C28" t="str">
+        <v>/api/admin/invoices/:id</v>
+      </c>
+      <c r="D28" t="str">
         <v>PUT</v>
       </c>
-      <c r="D28" t="str">
-        <v>/api/admin/invoices/:id</v>
-      </c>
       <c r="E28" t="str">
-        <v>Update invoice</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F28" t="str">
-        <v>/{id}</v>
+        <v>{ "status": "paid" }</v>
       </c>
       <c r="G28" t="str">
-        <v>{ "status": "paid" }</v>
+        <v>{ "message": "Invoice updated successfully" }</v>
       </c>
       <c r="H28" t="str">
-        <v>{ "message": "Invoice updated successfully" }</v>
-      </c>
-      <c r="I28">
-        <v>200</v>
-      </c>
-      <c r="J28" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Update invoice. Path params: {id}</v>
       </c>
     </row>
     <row r="29">
@@ -1592,28 +1670,25 @@
         <v>Admin</v>
       </c>
       <c r="C29" t="str">
+        <v>/api/admin/invoices/:id</v>
+      </c>
+      <c r="D29" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D29" t="str">
-        <v>/api/admin/invoices/:id</v>
-      </c>
       <c r="E29" t="str">
-        <v>Delete invoice</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F29" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>{ "message": "Invoice deleted successfully" }</v>
       </c>
       <c r="H29" t="str">
-        <v>{ "message": "Invoice deleted successfully" }</v>
-      </c>
-      <c r="I29">
-        <v>200</v>
-      </c>
-      <c r="J29" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Delete invoice. Path params: {id}</v>
       </c>
     </row>
     <row r="30">
@@ -1624,13 +1699,13 @@
         <v>Admin</v>
       </c>
       <c r="C30" t="str">
-        <v>GET</v>
+        <v>/api/admin/reviews</v>
       </c>
       <c r="D30" t="str">
-        <v>/api/admin/reviews</v>
+        <v>GET</v>
       </c>
       <c r="E30" t="str">
-        <v>List all reviews</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F30" t="str">
         <v/>
@@ -1638,11 +1713,11 @@
       <c r="G30" t="str">
         <v>{ "reviews": [...] }</v>
       </c>
-      <c r="H30">
-        <v>200</v>
+      <c r="H30" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I30" t="str">
-        <v>401/403/500</v>
+        <v>List all reviews. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="31">
@@ -1653,13 +1728,13 @@
         <v>Admin</v>
       </c>
       <c r="C31" t="str">
+        <v>/api/admin/reviews</v>
+      </c>
+      <c r="D31" t="str">
         <v>POST</v>
       </c>
-      <c r="D31" t="str">
-        <v>/api/admin/reviews</v>
-      </c>
       <c r="E31" t="str">
-        <v>Create review</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F31" t="str">
         <v>{ "customer": "&lt;custId&gt;", "package": "&lt;pkgId&gt;", "rating": 5 }</v>
@@ -1667,11 +1742,11 @@
       <c r="G31" t="str">
         <v>{ "message": "Review created successfully" }</v>
       </c>
-      <c r="H31">
-        <v>201</v>
+      <c r="H31" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I31" t="str">
-        <v>400/401/403/500</v>
+        <v>Create review</v>
       </c>
     </row>
     <row r="32">
@@ -1682,28 +1757,25 @@
         <v>Admin</v>
       </c>
       <c r="C32" t="str">
+        <v>/api/admin/reviews/:id</v>
+      </c>
+      <c r="D32" t="str">
         <v>PUT</v>
       </c>
-      <c r="D32" t="str">
-        <v>/api/admin/reviews/:id</v>
-      </c>
       <c r="E32" t="str">
-        <v>Update review</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F32" t="str">
-        <v>/{id}</v>
+        <v>{ "status": "approved" }</v>
       </c>
       <c r="G32" t="str">
-        <v>{ "status": "approved" }</v>
+        <v>{ "message": "Review updated successfully" }</v>
       </c>
       <c r="H32" t="str">
-        <v>{ "message": "Review updated successfully" }</v>
-      </c>
-      <c r="I32">
-        <v>200</v>
-      </c>
-      <c r="J32" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Update review. Path params: {id}</v>
       </c>
     </row>
     <row r="33">
@@ -1714,28 +1786,25 @@
         <v>Admin</v>
       </c>
       <c r="C33" t="str">
+        <v>/api/admin/reviews/:id</v>
+      </c>
+      <c r="D33" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D33" t="str">
-        <v>/api/admin/reviews/:id</v>
-      </c>
       <c r="E33" t="str">
-        <v>Delete review</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F33" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>{ "message": "Review deleted successfully" }</v>
       </c>
       <c r="H33" t="str">
-        <v>{ "message": "Review deleted successfully" }</v>
-      </c>
-      <c r="I33">
-        <v>200</v>
-      </c>
-      <c r="J33" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Delete review. Path params: {id}</v>
       </c>
     </row>
     <row r="34">
@@ -1746,13 +1815,13 @@
         <v>Admin</v>
       </c>
       <c r="C34" t="str">
-        <v>GET</v>
+        <v>/api/admin/coupons</v>
       </c>
       <c r="D34" t="str">
-        <v>/api/admin/coupons</v>
+        <v>GET</v>
       </c>
       <c r="E34" t="str">
-        <v>List all coupons</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F34" t="str">
         <v/>
@@ -1760,11 +1829,11 @@
       <c r="G34" t="str">
         <v>{ "coupons": [...] }</v>
       </c>
-      <c r="H34">
-        <v>200</v>
+      <c r="H34" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I34" t="str">
-        <v>401/403/500</v>
+        <v>List all coupons. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="35">
@@ -1775,13 +1844,13 @@
         <v>Admin</v>
       </c>
       <c r="C35" t="str">
+        <v>/api/admin/coupons</v>
+      </c>
+      <c r="D35" t="str">
         <v>POST</v>
       </c>
-      <c r="D35" t="str">
-        <v>/api/admin/coupons</v>
-      </c>
       <c r="E35" t="str">
-        <v>Create coupon</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F35" t="str">
         <v>{ "code": "SAVE10", "discount": 10, "type": "percentage", "minPurchase": 5000 }</v>
@@ -1789,11 +1858,11 @@
       <c r="G35" t="str">
         <v>{ "message": "Coupon created successfully" }</v>
       </c>
-      <c r="H35">
-        <v>201</v>
+      <c r="H35" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I35" t="str">
-        <v>400/401/403/500</v>
+        <v>Create coupon</v>
       </c>
     </row>
     <row r="36">
@@ -1804,28 +1873,25 @@
         <v>Admin</v>
       </c>
       <c r="C36" t="str">
+        <v>/api/admin/coupons/:id</v>
+      </c>
+      <c r="D36" t="str">
         <v>PUT</v>
       </c>
-      <c r="D36" t="str">
-        <v>/api/admin/coupons/:id</v>
-      </c>
       <c r="E36" t="str">
-        <v>Update coupon</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F36" t="str">
-        <v>/{id}</v>
+        <v>{ "discount": 15 }</v>
       </c>
       <c r="G36" t="str">
-        <v>{ "discount": 15 }</v>
+        <v>{ "message": "Coupon updated successfully" }</v>
       </c>
       <c r="H36" t="str">
-        <v>{ "message": "Coupon updated successfully" }</v>
-      </c>
-      <c r="I36">
-        <v>200</v>
-      </c>
-      <c r="J36" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Update coupon. Path params: {id}</v>
       </c>
     </row>
     <row r="37">
@@ -1836,28 +1902,25 @@
         <v>Admin</v>
       </c>
       <c r="C37" t="str">
+        <v>/api/admin/coupons/:id</v>
+      </c>
+      <c r="D37" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D37" t="str">
-        <v>/api/admin/coupons/:id</v>
-      </c>
       <c r="E37" t="str">
-        <v>Delete coupon</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F37" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G37" t="str">
-        <v/>
+        <v>{ "message": "Coupon deleted successfully" }</v>
       </c>
       <c r="H37" t="str">
-        <v>{ "message": "Coupon deleted successfully" }</v>
-      </c>
-      <c r="I37">
-        <v>200</v>
-      </c>
-      <c r="J37" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Delete coupon. Path params: {id}</v>
       </c>
     </row>
     <row r="38">
@@ -1868,13 +1931,13 @@
         <v>Admin</v>
       </c>
       <c r="C38" t="str">
-        <v>GET</v>
+        <v>/api/admin/settings</v>
       </c>
       <c r="D38" t="str">
-        <v>/api/admin/settings</v>
+        <v>GET</v>
       </c>
       <c r="E38" t="str">
-        <v>Get admin settings</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F38" t="str">
         <v/>
@@ -1882,11 +1945,11 @@
       <c r="G38" t="str">
         <v>{ "settings": {...} }</v>
       </c>
-      <c r="H38">
-        <v>200</v>
+      <c r="H38" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I38" t="str">
-        <v>401/403/500</v>
+        <v>Get admin settings</v>
       </c>
     </row>
     <row r="39">
@@ -1897,28 +1960,25 @@
         <v>Admin</v>
       </c>
       <c r="C39" t="str">
+        <v>/api/admin/settings</v>
+      </c>
+      <c r="D39" t="str">
         <v>PUT</v>
       </c>
-      <c r="D39" t="str">
-        <v>/api/admin/settings</v>
-      </c>
       <c r="E39" t="str">
+        <v>Bearer JWT (admin)</v>
+      </c>
+      <c r="F39" t="str">
+        <v>{ "currency": "INR", "language": "en" }</v>
+      </c>
+      <c r="G39" t="str">
+        <v>{ "message": "Settings updated" }</v>
+      </c>
+      <c r="H39" t="str">
+        <v>200 on success; 401/403/500 on error</v>
+      </c>
+      <c r="I39" t="str">
         <v>Update admin settings</v>
-      </c>
-      <c r="F39" t="str">
-        <v/>
-      </c>
-      <c r="G39" t="str">
-        <v>{ "currency": "INR", "language": "en" }</v>
-      </c>
-      <c r="H39" t="str">
-        <v>{ "message": "Settings updated" }</v>
-      </c>
-      <c r="I39">
-        <v>200</v>
-      </c>
-      <c r="J39" t="str">
-        <v>401/403/500</v>
       </c>
     </row>
     <row r="40">
@@ -1929,13 +1989,13 @@
         <v>Admin</v>
       </c>
       <c r="C40" t="str">
-        <v>GET</v>
+        <v>/api/admin/analytics</v>
       </c>
       <c r="D40" t="str">
-        <v>/api/admin/analytics</v>
+        <v>GET</v>
       </c>
       <c r="E40" t="str">
-        <v>Get admin analytics</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F40" t="str">
         <v/>
@@ -1943,11 +2003,11 @@
       <c r="G40" t="str">
         <v>{ "totalUsers": 100, "totalRevenue": 500000 }</v>
       </c>
-      <c r="H40">
-        <v>200</v>
+      <c r="H40" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I40" t="str">
-        <v>401/403/500</v>
+        <v>Get admin analytics</v>
       </c>
     </row>
     <row r="41">
@@ -1958,13 +2018,13 @@
         <v>Admin</v>
       </c>
       <c r="C41" t="str">
-        <v>GET</v>
+        <v>/api/admin/reports/summary</v>
       </c>
       <c r="D41" t="str">
-        <v>/api/admin/reports/summary</v>
+        <v>GET</v>
       </c>
       <c r="E41" t="str">
-        <v>Get report summary</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F41" t="str">
         <v/>
@@ -1972,11 +2032,11 @@
       <c r="G41" t="str">
         <v>{ "summary": {...} }</v>
       </c>
-      <c r="H41">
-        <v>200</v>
+      <c r="H41" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I41" t="str">
-        <v>401/403/500</v>
+        <v>Get report summary</v>
       </c>
     </row>
     <row r="42">
@@ -1987,13 +2047,13 @@
         <v>Admin</v>
       </c>
       <c r="C42" t="str">
-        <v>GET</v>
+        <v>/api/admin/notifications</v>
       </c>
       <c r="D42" t="str">
-        <v>/api/admin/notifications</v>
+        <v>GET</v>
       </c>
       <c r="E42" t="str">
-        <v>List admin notifications</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F42" t="str">
         <v/>
@@ -2001,11 +2061,11 @@
       <c r="G42" t="str">
         <v>{ "notifications": [...] }</v>
       </c>
-      <c r="H42">
-        <v>200</v>
+      <c r="H42" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I42" t="str">
-        <v>401/403/500</v>
+        <v>List admin notifications. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="43">
@@ -2016,13 +2076,13 @@
         <v>Admin</v>
       </c>
       <c r="C43" t="str">
+        <v>/api/admin/notifications</v>
+      </c>
+      <c r="D43" t="str">
         <v>POST</v>
       </c>
-      <c r="D43" t="str">
-        <v>/api/admin/notifications</v>
-      </c>
       <c r="E43" t="str">
-        <v>Send notification</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F43" t="str">
         <v>{ "title": "Update", "message": "Maintenance" }</v>
@@ -2030,11 +2090,11 @@
       <c r="G43" t="str">
         <v>{ "message": "Notification sent" }</v>
       </c>
-      <c r="H43">
-        <v>201</v>
+      <c r="H43" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I43" t="str">
-        <v>400/401/403/500</v>
+        <v>Send notification</v>
       </c>
     </row>
     <row r="44">
@@ -2045,28 +2105,25 @@
         <v>Admin</v>
       </c>
       <c r="C44" t="str">
+        <v>/api/admin/notifications/:id</v>
+      </c>
+      <c r="D44" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D44" t="str">
-        <v>/api/admin/notifications/:id</v>
-      </c>
       <c r="E44" t="str">
-        <v>Delete notification</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F44" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G44" t="str">
-        <v/>
+        <v>{ "message": "Notification deleted" }</v>
       </c>
       <c r="H44" t="str">
-        <v>{ "message": "Notification deleted" }</v>
-      </c>
-      <c r="I44">
-        <v>200</v>
-      </c>
-      <c r="J44" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Delete notification. Path params: {id}</v>
       </c>
     </row>
     <row r="45">
@@ -2077,68 +2134,135 @@
         <v>Admin</v>
       </c>
       <c r="C45" t="str">
+        <v>/api/admin/notifications/:id/read</v>
+      </c>
+      <c r="D45" t="str">
         <v>PUT</v>
       </c>
-      <c r="D45" t="str">
-        <v>/api/admin/notifications/:id/read</v>
-      </c>
       <c r="E45" t="str">
-        <v>Mark notification read</v>
+        <v>Bearer JWT (admin)</v>
       </c>
       <c r="F45" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G45" t="str">
-        <v/>
+        <v>{ "message": "Notification marked as read" }</v>
       </c>
       <c r="H45" t="str">
-        <v>{ "message": "Notification marked as read" }</v>
-      </c>
-      <c r="I45">
-        <v>200</v>
-      </c>
-      <c r="J45" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I45" t="str">
+        <v>Mark notification read. Path params: {id}</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>140</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Admin</v>
+      </c>
+      <c r="C46" t="str">
+        <v>/api/users</v>
+      </c>
+      <c r="D46" t="str">
+        <v>GET</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Bearer JWT (admin)</v>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v>{ "users": [{ "_id": "..." }] }</v>
+      </c>
+      <c r="H46" t="str">
+        <v>200 on success; 401/403/500 on error</v>
+      </c>
+      <c r="I46" t="str">
+        <v>List users (admin scoped). Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>141</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Admin</v>
+      </c>
+      <c r="C47" t="str">
+        <v>/api/admin/send-email</v>
+      </c>
+      <c r="D47" t="str">
+        <v>POST</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Bearer JWT (admin)</v>
+      </c>
+      <c r="F47" t="str">
+        <v>{ "to": "user@test.com", "subject": "Update", "message": "Body copy" }</v>
+      </c>
+      <c r="G47" t="str">
+        <v>{ "message": "Email sent" }</v>
+      </c>
+      <c r="H47" t="str">
+        <v>200 on success; 400/401/403/500 on error</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Send an email to a user</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I47"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I47"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:I32"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="46.83203125" customWidth="1"/>
+    <col min="7" max="7" width="46.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" customWidth="1"/>
+    <col min="9" max="9" width="52.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>S.No</v>
       </c>
       <c r="B1" t="str">
-        <v>Type of Dashboard</v>
+        <v>Dashboard Type</v>
       </c>
       <c r="C1" t="str">
-        <v>HTTP Method</v>
+        <v>API Endpoint</v>
       </c>
       <c r="D1" t="str">
-        <v>API Path</v>
+        <v>Method</v>
       </c>
       <c r="E1" t="str">
-        <v>Description</v>
+        <v>Auth</v>
       </c>
       <c r="F1" t="str">
-        <v>Sample Request Body (JSON)</v>
+        <v>Request Body</v>
       </c>
       <c r="G1" t="str">
-        <v>Sample Response (JSON)</v>
+        <v>Sample Response</v>
       </c>
       <c r="H1" t="str">
-        <v>Success Status Code</v>
+        <v>Status Codes</v>
       </c>
       <c r="I1" t="str">
-        <v>Error Status Codes</v>
+        <v>Notes</v>
       </c>
     </row>
     <row r="2">
@@ -2149,13 +2273,13 @@
         <v>Operator</v>
       </c>
       <c r="C2" t="str">
-        <v>GET</v>
+        <v>/api/operator/profile</v>
       </c>
       <c r="D2" t="str">
-        <v>/api/operator/profile</v>
+        <v>GET</v>
       </c>
       <c r="E2" t="str">
-        <v>Get operator profile</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -2163,11 +2287,11 @@
       <c r="G2" t="str">
         <v>{ "user": {...}, "profile": {...} }</v>
       </c>
-      <c r="H2">
-        <v>200</v>
+      <c r="H2" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I2" t="str">
-        <v>401/403/500</v>
+        <v>Get operator profile</v>
       </c>
     </row>
     <row r="3">
@@ -2178,28 +2302,25 @@
         <v>Operator</v>
       </c>
       <c r="C3" t="str">
+        <v>/api/operator/profile</v>
+      </c>
+      <c r="D3" t="str">
         <v>PUT</v>
       </c>
-      <c r="D3" t="str">
-        <v>/api/operator/profile</v>
-      </c>
       <c r="E3" t="str">
+        <v>Bearer JWT (tour_operator)</v>
+      </c>
+      <c r="F3" t="str">
+        <v>{ "fullName": "Updated Name", "phone": "9000000001" }</v>
+      </c>
+      <c r="G3" t="str">
+        <v>{ "message": "Profile updated" }</v>
+      </c>
+      <c r="H3" t="str">
+        <v>200 on success; 401/403/500 on error</v>
+      </c>
+      <c r="I3" t="str">
         <v>Update operator profile</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>{ "fullName": "Updated Name", "phone": "9000000001" }</v>
-      </c>
-      <c r="H3" t="str">
-        <v>{ "message": "Profile updated" }</v>
-      </c>
-      <c r="I3">
-        <v>200</v>
-      </c>
-      <c r="J3" t="str">
-        <v>401/403/500</v>
       </c>
     </row>
     <row r="4">
@@ -2210,13 +2331,13 @@
         <v>Operator</v>
       </c>
       <c r="C4" t="str">
-        <v>GET</v>
+        <v>/api/operator/packages</v>
       </c>
       <c r="D4" t="str">
-        <v>/api/operator/packages</v>
+        <v>GET</v>
       </c>
       <c r="E4" t="str">
-        <v>List operator packages</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -2224,11 +2345,11 @@
       <c r="G4" t="str">
         <v>{ "packages": [{ "_id": "..." }] }</v>
       </c>
-      <c r="H4">
-        <v>200</v>
+      <c r="H4" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I4" t="str">
-        <v>401/403/500</v>
+        <v>List operator packages. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="5">
@@ -2239,13 +2360,13 @@
         <v>Operator</v>
       </c>
       <c r="C5" t="str">
+        <v>/api/operator/packages</v>
+      </c>
+      <c r="D5" t="str">
         <v>POST</v>
       </c>
-      <c r="D5" t="str">
-        <v>/api/operator/packages</v>
-      </c>
       <c r="E5" t="str">
-        <v>Create package</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F5" t="str">
         <v>{ "name": "Goa Trip", "destination": "Goa", "duration": "3 Days", "price": 8000, "publishedStatus": "published" }</v>
@@ -2253,11 +2374,11 @@
       <c r="G5" t="str">
         <v>{ "message": "Package created successfully" }</v>
       </c>
-      <c r="H5">
-        <v>201</v>
+      <c r="H5" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I5" t="str">
-        <v>400/401/403/500</v>
+        <v>Create package</v>
       </c>
     </row>
     <row r="6">
@@ -2268,13 +2389,13 @@
         <v>Operator</v>
       </c>
       <c r="C6" t="str">
-        <v>GET</v>
+        <v>/api/operator/packages/:id</v>
       </c>
       <c r="D6" t="str">
-        <v>/api/operator/packages/:id</v>
+        <v>GET</v>
       </c>
       <c r="E6" t="str">
-        <v>Get single package</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F6" t="str">
         <v>/{packageId}</v>
@@ -2282,11 +2403,11 @@
       <c r="G6" t="str">
         <v>{ "package": {...} }</v>
       </c>
-      <c r="H6">
-        <v>200</v>
+      <c r="H6" t="str">
+        <v>200 on success; 404/401/403/500 on error</v>
       </c>
       <c r="I6" t="str">
-        <v>404/401/403/500</v>
+        <v>Get single package</v>
       </c>
     </row>
     <row r="7">
@@ -2297,28 +2418,25 @@
         <v>Operator</v>
       </c>
       <c r="C7" t="str">
+        <v>/api/operator/packages/:id</v>
+      </c>
+      <c r="D7" t="str">
         <v>PUT</v>
       </c>
-      <c r="D7" t="str">
-        <v>/api/operator/packages/:id</v>
-      </c>
       <c r="E7" t="str">
-        <v>Update package</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F7" t="str">
-        <v>/{packageId}</v>
+        <v>{ "price": 9500 }</v>
       </c>
       <c r="G7" t="str">
-        <v>{ "price": 9500 }</v>
+        <v>{ "message": "Package updated successfully" }</v>
       </c>
       <c r="H7" t="str">
-        <v>{ "message": "Package updated successfully" }</v>
-      </c>
-      <c r="I7">
-        <v>200</v>
-      </c>
-      <c r="J7" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Update package. Path params: {packageId}</v>
       </c>
     </row>
     <row r="8">
@@ -2329,28 +2447,25 @@
         <v>Operator</v>
       </c>
       <c r="C8" t="str">
+        <v>/api/operator/packages/:id</v>
+      </c>
+      <c r="D8" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D8" t="str">
-        <v>/api/operator/packages/:id</v>
-      </c>
       <c r="E8" t="str">
-        <v>Delete package</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F8" t="str">
-        <v>/{packageId}</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>{ "message": "Package deleted successfully" }</v>
       </c>
       <c r="H8" t="str">
-        <v>{ "message": "Package deleted successfully" }</v>
-      </c>
-      <c r="I8">
-        <v>200</v>
-      </c>
-      <c r="J8" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Delete package. Path params: {packageId}</v>
       </c>
     </row>
     <row r="9">
@@ -2361,13 +2476,13 @@
         <v>Operator</v>
       </c>
       <c r="C9" t="str">
-        <v>GET</v>
+        <v>/api/operator/itineraries</v>
       </c>
       <c r="D9" t="str">
-        <v>/api/operator/itineraries</v>
+        <v>GET</v>
       </c>
       <c r="E9" t="str">
-        <v>List itineraries</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -2375,11 +2490,11 @@
       <c r="G9" t="str">
         <v>{ "itineraries": [...] }</v>
       </c>
-      <c r="H9">
-        <v>200</v>
+      <c r="H9" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I9" t="str">
-        <v>401/403/500</v>
+        <v>List itineraries. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="10">
@@ -2390,13 +2505,13 @@
         <v>Operator</v>
       </c>
       <c r="C10" t="str">
-        <v>GET</v>
+        <v>/api/operator/itineraries/package/:packageId</v>
       </c>
       <c r="D10" t="str">
-        <v>/api/operator/itineraries/package/:packageId</v>
+        <v>GET</v>
       </c>
       <c r="E10" t="str">
-        <v>Get itineraries by package</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F10" t="str">
         <v>/{packageId}</v>
@@ -2404,11 +2519,11 @@
       <c r="G10" t="str">
         <v>{ "itineraries": [...] }</v>
       </c>
-      <c r="H10">
-        <v>200</v>
+      <c r="H10" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I10" t="str">
-        <v>401/403/500</v>
+        <v>Get itineraries by package</v>
       </c>
     </row>
     <row r="11">
@@ -2419,13 +2534,13 @@
         <v>Operator</v>
       </c>
       <c r="C11" t="str">
+        <v>/api/operator/itineraries</v>
+      </c>
+      <c r="D11" t="str">
         <v>POST</v>
       </c>
-      <c r="D11" t="str">
-        <v>/api/operator/itineraries</v>
-      </c>
       <c r="E11" t="str">
-        <v>Create itinerary</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F11" t="str">
         <v>{ "name": "Day 1", "packageId": "&lt;pkgId&gt;", "days": 4 }</v>
@@ -2433,11 +2548,11 @@
       <c r="G11" t="str">
         <v>{ "message": "Itinerary created successfully" }</v>
       </c>
-      <c r="H11">
-        <v>201</v>
+      <c r="H11" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I11" t="str">
-        <v>400/401/403/500</v>
+        <v>Create itinerary</v>
       </c>
     </row>
     <row r="12">
@@ -2448,28 +2563,25 @@
         <v>Operator</v>
       </c>
       <c r="C12" t="str">
+        <v>/api/operator/itineraries/:id</v>
+      </c>
+      <c r="D12" t="str">
         <v>PUT</v>
       </c>
-      <c r="D12" t="str">
-        <v>/api/operator/itineraries/:id</v>
-      </c>
       <c r="E12" t="str">
-        <v>Update itinerary</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F12" t="str">
-        <v>/{id}</v>
+        <v>{ "name": "Updated" }</v>
       </c>
       <c r="G12" t="str">
-        <v>{ "name": "Updated" }</v>
+        <v>{ "message": "Itinerary updated" }</v>
       </c>
       <c r="H12" t="str">
-        <v>{ "message": "Itinerary updated" }</v>
-      </c>
-      <c r="I12">
-        <v>200</v>
-      </c>
-      <c r="J12" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Update itinerary. Path params: {id}</v>
       </c>
     </row>
     <row r="13">
@@ -2480,28 +2592,25 @@
         <v>Operator</v>
       </c>
       <c r="C13" t="str">
+        <v>/api/operator/itineraries/:id</v>
+      </c>
+      <c r="D13" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D13" t="str">
-        <v>/api/operator/itineraries/:id</v>
-      </c>
       <c r="E13" t="str">
-        <v>Delete itinerary</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F13" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>{ "message": "Itinerary deleted" }</v>
       </c>
       <c r="H13" t="str">
-        <v>{ "message": "Itinerary deleted" }</v>
-      </c>
-      <c r="I13">
-        <v>200</v>
-      </c>
-      <c r="J13" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Delete itinerary. Path params: {id}</v>
       </c>
     </row>
     <row r="14">
@@ -2512,13 +2621,13 @@
         <v>Operator</v>
       </c>
       <c r="C14" t="str">
-        <v>GET</v>
+        <v>/api/operator/pricing/package/:packageId</v>
       </c>
       <c r="D14" t="str">
-        <v>/api/operator/pricing/package/:packageId</v>
+        <v>GET</v>
       </c>
       <c r="E14" t="str">
-        <v>Get pricing</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F14" t="str">
         <v>/{packageId}</v>
@@ -2526,11 +2635,11 @@
       <c r="G14" t="str">
         <v>{ "pricing": {...} }</v>
       </c>
-      <c r="H14">
-        <v>200</v>
+      <c r="H14" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I14" t="str">
-        <v>401/403/500</v>
+        <v>Get pricing</v>
       </c>
     </row>
     <row r="15">
@@ -2541,13 +2650,13 @@
         <v>Operator</v>
       </c>
       <c r="C15" t="str">
+        <v>/api/operator/pricing</v>
+      </c>
+      <c r="D15" t="str">
         <v>POST</v>
       </c>
-      <c r="D15" t="str">
-        <v>/api/operator/pricing</v>
-      </c>
       <c r="E15" t="str">
-        <v>Create pricing</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F15" t="str">
         <v>{ "packageId": "&lt;pkgId&gt;", "price": 5000 }</v>
@@ -2555,11 +2664,11 @@
       <c r="G15" t="str">
         <v>{ "message": "Pricing created" }</v>
       </c>
-      <c r="H15">
-        <v>201</v>
+      <c r="H15" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I15" t="str">
-        <v>400/401/403/500</v>
+        <v>Create pricing</v>
       </c>
     </row>
     <row r="16">
@@ -2570,28 +2679,25 @@
         <v>Operator</v>
       </c>
       <c r="C16" t="str">
+        <v>/api/operator/pricing/:id</v>
+      </c>
+      <c r="D16" t="str">
         <v>PUT</v>
       </c>
-      <c r="D16" t="str">
-        <v>/api/operator/pricing/:id</v>
-      </c>
       <c r="E16" t="str">
-        <v>Update pricing</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F16" t="str">
-        <v>/{id}</v>
+        <v>{ "price": 5500 }</v>
       </c>
       <c r="G16" t="str">
-        <v>{ "price": 5500 }</v>
+        <v>{ "message": "Pricing updated" }</v>
       </c>
       <c r="H16" t="str">
-        <v>{ "message": "Pricing updated" }</v>
-      </c>
-      <c r="I16">
-        <v>200</v>
-      </c>
-      <c r="J16" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Update pricing. Path params: {id}</v>
       </c>
     </row>
     <row r="17">
@@ -2602,13 +2708,13 @@
         <v>Operator</v>
       </c>
       <c r="C17" t="str">
-        <v>GET</v>
+        <v>/api/operator/availability/package/:packageId</v>
       </c>
       <c r="D17" t="str">
-        <v>/api/operator/availability/package/:packageId</v>
+        <v>GET</v>
       </c>
       <c r="E17" t="str">
-        <v>Get availability</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F17" t="str">
         <v>/{packageId}</v>
@@ -2616,11 +2722,11 @@
       <c r="G17" t="str">
         <v>{ "availability": [...] }</v>
       </c>
-      <c r="H17">
-        <v>200</v>
+      <c r="H17" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I17" t="str">
-        <v>401/403/500</v>
+        <v>Get availability. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2737,13 @@
         <v>Operator</v>
       </c>
       <c r="C18" t="str">
+        <v>/api/operator/availability</v>
+      </c>
+      <c r="D18" t="str">
         <v>POST</v>
       </c>
-      <c r="D18" t="str">
-        <v>/api/operator/availability</v>
-      </c>
       <c r="E18" t="str">
-        <v>Create availability</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F18" t="str">
         <v>{ "packageId": "&lt;pkgId&gt;", "date": "2026-12-25", "available": 20 }</v>
@@ -2645,11 +2751,11 @@
       <c r="G18" t="str">
         <v>{ "message": "Availability created" }</v>
       </c>
-      <c r="H18">
-        <v>201</v>
+      <c r="H18" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I18" t="str">
-        <v>400/401/403/500</v>
+        <v>Create availability</v>
       </c>
     </row>
     <row r="19">
@@ -2660,28 +2766,25 @@
         <v>Operator</v>
       </c>
       <c r="C19" t="str">
+        <v>/api/operator/availability/:id</v>
+      </c>
+      <c r="D19" t="str">
         <v>PUT</v>
       </c>
-      <c r="D19" t="str">
-        <v>/api/operator/availability/:id</v>
-      </c>
       <c r="E19" t="str">
-        <v>Update availability</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F19" t="str">
-        <v>/{id}</v>
+        <v>{ "available": 15 }</v>
       </c>
       <c r="G19" t="str">
-        <v>{ "available": 15 }</v>
+        <v>{ "message": "Availability updated" }</v>
       </c>
       <c r="H19" t="str">
-        <v>{ "message": "Availability updated" }</v>
-      </c>
-      <c r="I19">
-        <v>200</v>
-      </c>
-      <c r="J19" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Update availability. Path params: {id}</v>
       </c>
     </row>
     <row r="20">
@@ -2692,28 +2795,25 @@
         <v>Operator</v>
       </c>
       <c r="C20" t="str">
+        <v>/api/operator/availability/:id</v>
+      </c>
+      <c r="D20" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D20" t="str">
-        <v>/api/operator/availability/:id</v>
-      </c>
       <c r="E20" t="str">
-        <v>Delete availability</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F20" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>{ "message": "Availability deleted" }</v>
       </c>
       <c r="H20" t="str">
-        <v>{ "message": "Availability deleted" }</v>
-      </c>
-      <c r="I20">
-        <v>200</v>
-      </c>
-      <c r="J20" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Delete availability. Path params: {id}</v>
       </c>
     </row>
     <row r="21">
@@ -2724,13 +2824,13 @@
         <v>Operator</v>
       </c>
       <c r="C21" t="str">
-        <v>GET</v>
+        <v>/api/operator/bookings</v>
       </c>
       <c r="D21" t="str">
-        <v>/api/operator/bookings</v>
+        <v>GET</v>
       </c>
       <c r="E21" t="str">
-        <v>List bookings</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -2738,11 +2838,11 @@
       <c r="G21" t="str">
         <v>{ "bookings": [...] }</v>
       </c>
-      <c r="H21">
-        <v>200</v>
+      <c r="H21" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I21" t="str">
-        <v>401/403/500</v>
+        <v>List bookings. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="22">
@@ -2753,13 +2853,13 @@
         <v>Operator</v>
       </c>
       <c r="C22" t="str">
-        <v>GET</v>
+        <v>/api/operator/bookings/:id</v>
       </c>
       <c r="D22" t="str">
-        <v>/api/operator/bookings/:id</v>
+        <v>GET</v>
       </c>
       <c r="E22" t="str">
-        <v>Get booking details</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F22" t="str">
         <v>/{id}</v>
@@ -2767,11 +2867,11 @@
       <c r="G22" t="str">
         <v>{ "booking": {...} }</v>
       </c>
-      <c r="H22">
-        <v>200</v>
+      <c r="H22" t="str">
+        <v>200 on success; 404/401/403/500 on error</v>
       </c>
       <c r="I22" t="str">
-        <v>404/401/403/500</v>
+        <v>Get booking details</v>
       </c>
     </row>
     <row r="23">
@@ -2782,28 +2882,25 @@
         <v>Operator</v>
       </c>
       <c r="C23" t="str">
+        <v>/api/operator/bookings/:id</v>
+      </c>
+      <c r="D23" t="str">
         <v>PUT</v>
       </c>
-      <c r="D23" t="str">
-        <v>/api/operator/bookings/:id</v>
-      </c>
       <c r="E23" t="str">
-        <v>Update booking</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F23" t="str">
-        <v>/{id}</v>
+        <v>{ "status": "confirmed" }</v>
       </c>
       <c r="G23" t="str">
-        <v>{ "status": "confirmed" }</v>
+        <v>{ "message": "Booking updated" }</v>
       </c>
       <c r="H23" t="str">
-        <v>{ "message": "Booking updated" }</v>
-      </c>
-      <c r="I23">
-        <v>200</v>
-      </c>
-      <c r="J23" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Update booking. Path params: {id}</v>
       </c>
     </row>
     <row r="24">
@@ -2814,13 +2911,13 @@
         <v>Operator</v>
       </c>
       <c r="C24" t="str">
-        <v>GET</v>
+        <v>/api/operator/customers</v>
       </c>
       <c r="D24" t="str">
-        <v>/api/operator/customers</v>
+        <v>GET</v>
       </c>
       <c r="E24" t="str">
-        <v>List customers</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -2828,11 +2925,11 @@
       <c r="G24" t="str">
         <v>{ "customers": [...] }</v>
       </c>
-      <c r="H24">
-        <v>200</v>
+      <c r="H24" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I24" t="str">
-        <v>401/403/500</v>
+        <v>List customers. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="25">
@@ -2843,13 +2940,13 @@
         <v>Operator</v>
       </c>
       <c r="C25" t="str">
-        <v>GET</v>
+        <v>/api/operator/customers/:id</v>
       </c>
       <c r="D25" t="str">
-        <v>/api/operator/customers/:id</v>
+        <v>GET</v>
       </c>
       <c r="E25" t="str">
-        <v>Get customer details</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F25" t="str">
         <v>/{id}</v>
@@ -2857,11 +2954,11 @@
       <c r="G25" t="str">
         <v>{ "bookings": [...], "reviews": [...] }</v>
       </c>
-      <c r="H25">
-        <v>200</v>
+      <c r="H25" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I25" t="str">
-        <v>401/403/500</v>
+        <v>Get customer details</v>
       </c>
     </row>
     <row r="26">
@@ -2872,13 +2969,13 @@
         <v>Operator</v>
       </c>
       <c r="C26" t="str">
-        <v>GET</v>
+        <v>/api/operator/reviews</v>
       </c>
       <c r="D26" t="str">
-        <v>/api/operator/reviews</v>
+        <v>GET</v>
       </c>
       <c r="E26" t="str">
-        <v>List reviews</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -2886,11 +2983,11 @@
       <c r="G26" t="str">
         <v>{ "reviews": [...] }</v>
       </c>
-      <c r="H26">
-        <v>200</v>
+      <c r="H26" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I26" t="str">
-        <v>401/403/500</v>
+        <v>List reviews. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="27">
@@ -2901,28 +2998,25 @@
         <v>Operator</v>
       </c>
       <c r="C27" t="str">
+        <v>/api/operator/reviews/:id/respond</v>
+      </c>
+      <c r="D27" t="str">
         <v>PUT</v>
       </c>
-      <c r="D27" t="str">
-        <v>/api/operator/reviews/:id/respond</v>
-      </c>
       <c r="E27" t="str">
-        <v>Respond to review</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F27" t="str">
-        <v>/{id}</v>
+        <v>{ "response": "Thank you!" }</v>
       </c>
       <c r="G27" t="str">
-        <v>{ "response": "Thank you!" }</v>
+        <v>{ "message": "Review responded" }</v>
       </c>
       <c r="H27" t="str">
-        <v>{ "message": "Review responded" }</v>
-      </c>
-      <c r="I27">
-        <v>200</v>
-      </c>
-      <c r="J27" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Respond to review. Path params: {id}</v>
       </c>
     </row>
     <row r="28">
@@ -2933,13 +3027,13 @@
         <v>Operator</v>
       </c>
       <c r="C28" t="str">
-        <v>GET</v>
+        <v>/api/operator/revenue</v>
       </c>
       <c r="D28" t="str">
-        <v>/api/operator/revenue</v>
+        <v>GET</v>
       </c>
       <c r="E28" t="str">
-        <v>Get revenue report</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -2947,11 +3041,11 @@
       <c r="G28" t="str">
         <v>{ "totalRevenue": 500000, "revenueByPackage": [] }</v>
       </c>
-      <c r="H28">
-        <v>200</v>
+      <c r="H28" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I28" t="str">
-        <v>401/403/500</v>
+        <v>Get revenue report</v>
       </c>
     </row>
     <row r="29">
@@ -2962,13 +3056,13 @@
         <v>Operator</v>
       </c>
       <c r="C29" t="str">
-        <v>GET</v>
+        <v>/api/operator/notifications</v>
       </c>
       <c r="D29" t="str">
-        <v>/api/operator/notifications</v>
+        <v>GET</v>
       </c>
       <c r="E29" t="str">
-        <v>List notifications</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -2976,11 +3070,11 @@
       <c r="G29" t="str">
         <v>{ "notifications": [...] }</v>
       </c>
-      <c r="H29">
-        <v>200</v>
+      <c r="H29" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I29" t="str">
-        <v>401/403/500</v>
+        <v>List notifications. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="30">
@@ -2991,28 +3085,25 @@
         <v>Operator</v>
       </c>
       <c r="C30" t="str">
+        <v>/api/operator/notifications/:id/read</v>
+      </c>
+      <c r="D30" t="str">
         <v>PUT</v>
       </c>
-      <c r="D30" t="str">
-        <v>/api/operator/notifications/:id/read</v>
-      </c>
       <c r="E30" t="str">
-        <v>Mark notification read</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F30" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>{ "message": "Notification marked as read" }</v>
       </c>
       <c r="H30" t="str">
-        <v>{ "message": "Notification marked as read" }</v>
-      </c>
-      <c r="I30">
-        <v>200</v>
-      </c>
-      <c r="J30" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Mark notification read. Path params: {id}</v>
       </c>
     </row>
     <row r="31">
@@ -3023,13 +3114,13 @@
         <v>Operator</v>
       </c>
       <c r="C31" t="str">
+        <v>/api/operator/notifications/read-all</v>
+      </c>
+      <c r="D31" t="str">
         <v>PUT</v>
       </c>
-      <c r="D31" t="str">
-        <v>/api/operator/notifications/read-all</v>
-      </c>
       <c r="E31" t="str">
-        <v>Mark all read</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F31" t="str">
         <v/>
@@ -3037,11 +3128,11 @@
       <c r="G31" t="str">
         <v>{ "message": "All marked as read" }</v>
       </c>
-      <c r="H31">
-        <v>200</v>
+      <c r="H31" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I31" t="str">
-        <v>401/403/500</v>
+        <v>Mark all read</v>
       </c>
     </row>
     <row r="32">
@@ -3052,68 +3143,77 @@
         <v>Operator</v>
       </c>
       <c r="C32" t="str">
+        <v>/api/operator/notifications/:id</v>
+      </c>
+      <c r="D32" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D32" t="str">
-        <v>/api/operator/notifications/:id</v>
-      </c>
       <c r="E32" t="str">
-        <v>Delete notification</v>
+        <v>Bearer JWT (tour_operator)</v>
       </c>
       <c r="F32" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>{ "message": "Notification deleted" }</v>
       </c>
       <c r="H32" t="str">
-        <v>{ "message": "Notification deleted" }</v>
-      </c>
-      <c r="I32">
-        <v>200</v>
-      </c>
-      <c r="J32" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Delete notification. Path params: {id}</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I32"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I32"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:I23"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="46.83203125" customWidth="1"/>
+    <col min="7" max="7" width="46.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" customWidth="1"/>
+    <col min="9" max="9" width="52.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>S.No</v>
       </c>
       <c r="B1" t="str">
-        <v>Type of Dashboard</v>
+        <v>Dashboard Type</v>
       </c>
       <c r="C1" t="str">
-        <v>HTTP Method</v>
+        <v>API Endpoint</v>
       </c>
       <c r="D1" t="str">
-        <v>API Path</v>
+        <v>Method</v>
       </c>
       <c r="E1" t="str">
-        <v>Description</v>
+        <v>Auth</v>
       </c>
       <c r="F1" t="str">
-        <v>Sample Request Body (JSON)</v>
+        <v>Request Body</v>
       </c>
       <c r="G1" t="str">
-        <v>Sample Response (JSON)</v>
+        <v>Sample Response</v>
       </c>
       <c r="H1" t="str">
-        <v>Success Status Code</v>
+        <v>Status Codes</v>
       </c>
       <c r="I1" t="str">
-        <v>Error Status Codes</v>
+        <v>Notes</v>
       </c>
     </row>
     <row r="2">
@@ -3124,13 +3224,13 @@
         <v>Customer</v>
       </c>
       <c r="C2" t="str">
-        <v>GET</v>
+        <v>/api/customer/profile</v>
       </c>
       <c r="D2" t="str">
-        <v>/api/customer/profile</v>
+        <v>GET</v>
       </c>
       <c r="E2" t="str">
-        <v>Get customer profile</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -3138,11 +3238,11 @@
       <c r="G2" t="str">
         <v>{ "user": {...} }</v>
       </c>
-      <c r="H2">
-        <v>200</v>
+      <c r="H2" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I2" t="str">
-        <v>401/403/500</v>
+        <v>Get customer profile</v>
       </c>
     </row>
     <row r="3">
@@ -3153,28 +3253,25 @@
         <v>Customer</v>
       </c>
       <c r="C3" t="str">
+        <v>/api/customer/profile</v>
+      </c>
+      <c r="D3" t="str">
         <v>PUT</v>
       </c>
-      <c r="D3" t="str">
-        <v>/api/customer/profile</v>
-      </c>
       <c r="E3" t="str">
+        <v>Bearer JWT (customer)</v>
+      </c>
+      <c r="F3" t="str">
+        <v>{ "fullName": "Jane", "phone": "9000000001" }</v>
+      </c>
+      <c r="G3" t="str">
+        <v>{ "message": "Profile updated" }</v>
+      </c>
+      <c r="H3" t="str">
+        <v>200 on success; 401/403/500 on error</v>
+      </c>
+      <c r="I3" t="str">
         <v>Update profile</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>{ "fullName": "Jane", "phone": "9000000001" }</v>
-      </c>
-      <c r="H3" t="str">
-        <v>{ "message": "Profile updated" }</v>
-      </c>
-      <c r="I3">
-        <v>200</v>
-      </c>
-      <c r="J3" t="str">
-        <v>401/403/500</v>
       </c>
     </row>
     <row r="4">
@@ -3185,13 +3282,13 @@
         <v>Customer</v>
       </c>
       <c r="C4" t="str">
-        <v>GET</v>
+        <v>/api/customer/packages</v>
       </c>
       <c r="D4" t="str">
-        <v>/api/customer/packages</v>
+        <v>GET</v>
       </c>
       <c r="E4" t="str">
-        <v>List packages for customer</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -3199,11 +3296,11 @@
       <c r="G4" t="str">
         <v>{ "packages": [...] }</v>
       </c>
-      <c r="H4">
-        <v>200</v>
+      <c r="H4" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I4" t="str">
-        <v>401/403/500</v>
+        <v>List packages for customer. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="5">
@@ -3214,13 +3311,13 @@
         <v>Customer</v>
       </c>
       <c r="C5" t="str">
-        <v>GET</v>
+        <v>/api/customer/bookings</v>
       </c>
       <c r="D5" t="str">
-        <v>/api/customer/bookings</v>
+        <v>GET</v>
       </c>
       <c r="E5" t="str">
-        <v>List bookings</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -3228,11 +3325,11 @@
       <c r="G5" t="str">
         <v>{ "bookings": [...] }</v>
       </c>
-      <c r="H5">
-        <v>200</v>
+      <c r="H5" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I5" t="str">
-        <v>401/403/500</v>
+        <v>List bookings. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="6">
@@ -3243,13 +3340,13 @@
         <v>Customer</v>
       </c>
       <c r="C6" t="str">
+        <v>/api/customer/bookings</v>
+      </c>
+      <c r="D6" t="str">
         <v>POST</v>
       </c>
-      <c r="D6" t="str">
-        <v>/api/customer/bookings</v>
-      </c>
       <c r="E6" t="str">
-        <v>Create booking</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F6" t="str">
         <v>{ "packageId": "&lt;pkgId&gt;", "travelers": 2, "travelDate": "2026-12-25" }</v>
@@ -3257,11 +3354,11 @@
       <c r="G6" t="str">
         <v>{ "message": "Booking created" }</v>
       </c>
-      <c r="H6">
-        <v>201</v>
+      <c r="H6" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I6" t="str">
-        <v>400/401/403/500</v>
+        <v>Create booking</v>
       </c>
     </row>
     <row r="7">
@@ -3272,13 +3369,13 @@
         <v>Customer</v>
       </c>
       <c r="C7" t="str">
-        <v>GET</v>
+        <v>/api/customer/bookings/:id</v>
       </c>
       <c r="D7" t="str">
-        <v>/api/customer/bookings/:id</v>
+        <v>GET</v>
       </c>
       <c r="E7" t="str">
-        <v>Get booking details</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F7" t="str">
         <v>/{id}</v>
@@ -3286,11 +3383,11 @@
       <c r="G7" t="str">
         <v>{ "booking": {...} }</v>
       </c>
-      <c r="H7">
-        <v>200</v>
+      <c r="H7" t="str">
+        <v>200 on success; 404/401/403/500 on error</v>
       </c>
       <c r="I7" t="str">
-        <v>404/401/403/500</v>
+        <v>Get booking details</v>
       </c>
     </row>
     <row r="8">
@@ -3301,28 +3398,25 @@
         <v>Customer</v>
       </c>
       <c r="C8" t="str">
+        <v>/api/customer/bookings/:id</v>
+      </c>
+      <c r="D8" t="str">
         <v>PUT</v>
       </c>
-      <c r="D8" t="str">
-        <v>/api/customer/bookings/:id</v>
-      </c>
       <c r="E8" t="str">
-        <v>Update booking</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F8" t="str">
-        <v>/{id}</v>
+        <v>{ "phone": "9000000099" }</v>
       </c>
       <c r="G8" t="str">
-        <v>{ "phone": "9000000099" }</v>
+        <v>{ "message": "Booking updated" }</v>
       </c>
       <c r="H8" t="str">
-        <v>{ "message": "Booking updated" }</v>
-      </c>
-      <c r="I8">
-        <v>200</v>
-      </c>
-      <c r="J8" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Update booking. Path params: {id}</v>
       </c>
     </row>
     <row r="9">
@@ -3333,28 +3427,25 @@
         <v>Customer</v>
       </c>
       <c r="C9" t="str">
+        <v>/api/customer/bookings/:id/pay</v>
+      </c>
+      <c r="D9" t="str">
         <v>PUT</v>
       </c>
-      <c r="D9" t="str">
-        <v>/api/customer/bookings/:id/pay</v>
-      </c>
       <c r="E9" t="str">
-        <v>Pay for booking</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F9" t="str">
-        <v>/{id}</v>
+        <v>{ "paidAmount": 12000 }</v>
       </c>
       <c r="G9" t="str">
-        <v>{ "paidAmount": 12000 }</v>
+        <v>{ "message": "Payment successful" }</v>
       </c>
       <c r="H9" t="str">
-        <v>{ "message": "Payment successful" }</v>
-      </c>
-      <c r="I9">
-        <v>200</v>
-      </c>
-      <c r="J9" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Pay for booking. Path params: {id}</v>
       </c>
     </row>
     <row r="10">
@@ -3365,13 +3456,13 @@
         <v>Customer</v>
       </c>
       <c r="C10" t="str">
-        <v>GET</v>
+        <v>/api/customer/itineraries</v>
       </c>
       <c r="D10" t="str">
-        <v>/api/customer/itineraries</v>
+        <v>GET</v>
       </c>
       <c r="E10" t="str">
-        <v>Get itineraries</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -3379,11 +3470,11 @@
       <c r="G10" t="str">
         <v>{ "itineraries": [...] }</v>
       </c>
-      <c r="H10">
-        <v>200</v>
+      <c r="H10" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I10" t="str">
-        <v>401/403/500</v>
+        <v>Get itineraries. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="11">
@@ -3394,13 +3485,13 @@
         <v>Customer</v>
       </c>
       <c r="C11" t="str">
-        <v>GET</v>
+        <v>/api/customer/invoices</v>
       </c>
       <c r="D11" t="str">
-        <v>/api/customer/invoices</v>
+        <v>GET</v>
       </c>
       <c r="E11" t="str">
-        <v>List invoices</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -3408,11 +3499,11 @@
       <c r="G11" t="str">
         <v>{ "invoices": [...] }</v>
       </c>
-      <c r="H11">
-        <v>200</v>
+      <c r="H11" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I11" t="str">
-        <v>401/403/500</v>
+        <v>List invoices. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="12">
@@ -3423,13 +3514,13 @@
         <v>Customer</v>
       </c>
       <c r="C12" t="str">
-        <v>GET</v>
+        <v>/api/customer/invoices/:id</v>
       </c>
       <c r="D12" t="str">
-        <v>/api/customer/invoices/:id</v>
+        <v>GET</v>
       </c>
       <c r="E12" t="str">
-        <v>Get invoice details</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F12" t="str">
         <v>/{id}</v>
@@ -3437,11 +3528,11 @@
       <c r="G12" t="str">
         <v>{ "invoice": {...} }</v>
       </c>
-      <c r="H12">
-        <v>200</v>
+      <c r="H12" t="str">
+        <v>200 on success; 404/401/403/500 on error</v>
       </c>
       <c r="I12" t="str">
-        <v>404/401/403/500</v>
+        <v>Get invoice details</v>
       </c>
     </row>
     <row r="13">
@@ -3452,13 +3543,13 @@
         <v>Customer</v>
       </c>
       <c r="C13" t="str">
-        <v>GET</v>
+        <v>/api/customer/reviews</v>
       </c>
       <c r="D13" t="str">
-        <v>/api/customer/reviews</v>
+        <v>GET</v>
       </c>
       <c r="E13" t="str">
-        <v>List reviews</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -3466,11 +3557,11 @@
       <c r="G13" t="str">
         <v>{ "reviews": [...] }</v>
       </c>
-      <c r="H13">
-        <v>200</v>
+      <c r="H13" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I13" t="str">
-        <v>401/403/500</v>
+        <v>List reviews. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="14">
@@ -3481,13 +3572,13 @@
         <v>Customer</v>
       </c>
       <c r="C14" t="str">
+        <v>/api/customer/reviews</v>
+      </c>
+      <c r="D14" t="str">
         <v>POST</v>
       </c>
-      <c r="D14" t="str">
-        <v>/api/customer/reviews</v>
-      </c>
       <c r="E14" t="str">
-        <v>Create review</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F14" t="str">
         <v>{ "packageId": "&lt;pkgId&gt;", "rating": 5, "title": "Amazing", "comment": "Great" }</v>
@@ -3495,11 +3586,11 @@
       <c r="G14" t="str">
         <v>{ "message": "Review created" }</v>
       </c>
-      <c r="H14">
-        <v>201</v>
+      <c r="H14" t="str">
+        <v>201 on success; 400/401/403/500 on error</v>
       </c>
       <c r="I14" t="str">
-        <v>400/401/403/500</v>
+        <v>Create review</v>
       </c>
     </row>
     <row r="15">
@@ -3510,28 +3601,25 @@
         <v>Customer</v>
       </c>
       <c r="C15" t="str">
+        <v>/api/customer/reviews/:id</v>
+      </c>
+      <c r="D15" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D15" t="str">
-        <v>/api/customer/reviews/:id</v>
-      </c>
       <c r="E15" t="str">
-        <v>Delete review</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F15" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>{ "message": "Review deleted" }</v>
       </c>
       <c r="H15" t="str">
-        <v>{ "message": "Review deleted" }</v>
-      </c>
-      <c r="I15">
-        <v>200</v>
-      </c>
-      <c r="J15" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Delete review. Path params: {id}</v>
       </c>
     </row>
     <row r="16">
@@ -3542,13 +3630,13 @@
         <v>Customer</v>
       </c>
       <c r="C16" t="str">
-        <v>GET</v>
+        <v>/api/customer/wishlist</v>
       </c>
       <c r="D16" t="str">
-        <v>/api/customer/wishlist</v>
+        <v>GET</v>
       </c>
       <c r="E16" t="str">
-        <v>List wishlist</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -3556,11 +3644,11 @@
       <c r="G16" t="str">
         <v>{ "wishlist": [...] }</v>
       </c>
-      <c r="H16">
-        <v>200</v>
+      <c r="H16" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I16" t="str">
-        <v>401/403/500</v>
+        <v>List wishlist. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="17">
@@ -3571,13 +3659,13 @@
         <v>Customer</v>
       </c>
       <c r="C17" t="str">
+        <v>/api/customer/wishlist</v>
+      </c>
+      <c r="D17" t="str">
         <v>POST</v>
       </c>
-      <c r="D17" t="str">
-        <v>/api/customer/wishlist</v>
-      </c>
       <c r="E17" t="str">
-        <v>Add to wishlist</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F17" t="str">
         <v>{ "packageId": "&lt;pkgId&gt;" }</v>
@@ -3585,11 +3673,11 @@
       <c r="G17" t="str">
         <v>{ "message": "Added to wishlist" }</v>
       </c>
-      <c r="H17">
-        <v>201</v>
+      <c r="H17" t="str">
+        <v>201 on success; 401/403/400/500 on error</v>
       </c>
       <c r="I17" t="str">
-        <v>401/403/400/500</v>
+        <v>Add to wishlist</v>
       </c>
     </row>
     <row r="18">
@@ -3600,28 +3688,25 @@
         <v>Customer</v>
       </c>
       <c r="C18" t="str">
+        <v>/api/customer/wishlist/:id</v>
+      </c>
+      <c r="D18" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D18" t="str">
-        <v>/api/customer/wishlist/:id</v>
-      </c>
       <c r="E18" t="str">
-        <v>Remove from wishlist</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F18" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>{ "message": "Removed from wishlist" }</v>
       </c>
       <c r="H18" t="str">
-        <v>{ "message": "Removed from wishlist" }</v>
-      </c>
-      <c r="I18">
-        <v>200</v>
-      </c>
-      <c r="J18" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Remove from wishlist. Path params: {id}</v>
       </c>
     </row>
     <row r="19">
@@ -3632,13 +3717,13 @@
         <v>Customer</v>
       </c>
       <c r="C19" t="str">
-        <v>GET</v>
+        <v>/api/customer/notifications</v>
       </c>
       <c r="D19" t="str">
-        <v>/api/customer/notifications</v>
+        <v>GET</v>
       </c>
       <c r="E19" t="str">
-        <v>List notifications</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -3646,11 +3731,11 @@
       <c r="G19" t="str">
         <v>{ "notifications": [...] }</v>
       </c>
-      <c r="H19">
-        <v>200</v>
+      <c r="H19" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I19" t="str">
-        <v>401/403/500</v>
+        <v>List notifications. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="20">
@@ -3661,28 +3746,25 @@
         <v>Customer</v>
       </c>
       <c r="C20" t="str">
+        <v>/api/customer/notifications/:id/read</v>
+      </c>
+      <c r="D20" t="str">
         <v>PUT</v>
       </c>
-      <c r="D20" t="str">
-        <v>/api/customer/notifications/:id/read</v>
-      </c>
       <c r="E20" t="str">
-        <v>Mark notification read</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F20" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>{ "message": "Notification marked as read" }</v>
       </c>
       <c r="H20" t="str">
-        <v>{ "message": "Notification marked as read" }</v>
-      </c>
-      <c r="I20">
-        <v>200</v>
-      </c>
-      <c r="J20" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Mark notification read. Path params: {id}</v>
       </c>
     </row>
     <row r="21">
@@ -3693,13 +3775,13 @@
         <v>Customer</v>
       </c>
       <c r="C21" t="str">
+        <v>/api/customer/notifications/read-all</v>
+      </c>
+      <c r="D21" t="str">
         <v>PUT</v>
       </c>
-      <c r="D21" t="str">
-        <v>/api/customer/notifications/read-all</v>
-      </c>
       <c r="E21" t="str">
-        <v>Mark all read</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -3707,11 +3789,11 @@
       <c r="G21" t="str">
         <v>{ "message": "All marked as read" }</v>
       </c>
-      <c r="H21">
-        <v>200</v>
+      <c r="H21" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I21" t="str">
-        <v>401/403/500</v>
+        <v>Mark all read</v>
       </c>
     </row>
     <row r="22">
@@ -3722,28 +3804,25 @@
         <v>Customer</v>
       </c>
       <c r="C22" t="str">
+        <v>/api/customer/notifications/:id</v>
+      </c>
+      <c r="D22" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D22" t="str">
-        <v>/api/customer/notifications/:id</v>
-      </c>
       <c r="E22" t="str">
-        <v>Delete notification</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F22" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>{ "message": "Notification deleted" }</v>
       </c>
       <c r="H22" t="str">
-        <v>{ "message": "Notification deleted" }</v>
-      </c>
-      <c r="I22">
-        <v>200</v>
-      </c>
-      <c r="J22" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Delete notification. Path params: {id}</v>
       </c>
     </row>
     <row r="23">
@@ -3754,13 +3833,13 @@
         <v>Customer</v>
       </c>
       <c r="C23" t="str">
-        <v>GET</v>
+        <v>/api/customer/analytics</v>
       </c>
       <c r="D23" t="str">
-        <v>/api/customer/analytics</v>
+        <v>GET</v>
       </c>
       <c r="E23" t="str">
-        <v>Get analytics</v>
+        <v>Bearer JWT (customer)</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -3768,51 +3847,63 @@
       <c r="G23" t="str">
         <v>{ "stats": {...} }</v>
       </c>
-      <c r="H23">
-        <v>200</v>
+      <c r="H23" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I23" t="str">
-        <v>401/403/500</v>
+        <v>Get analytics</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I23"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I23"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:I29"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="46.83203125" customWidth="1"/>
+    <col min="7" max="7" width="46.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" customWidth="1"/>
+    <col min="9" max="9" width="52.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>S.No</v>
       </c>
       <c r="B1" t="str">
-        <v>Type of Dashboard</v>
+        <v>Dashboard Type</v>
       </c>
       <c r="C1" t="str">
-        <v>HTTP Method</v>
+        <v>API Endpoint</v>
       </c>
       <c r="D1" t="str">
-        <v>API Path</v>
+        <v>Method</v>
       </c>
       <c r="E1" t="str">
-        <v>Description</v>
+        <v>Auth</v>
       </c>
       <c r="F1" t="str">
-        <v>Sample Request Body (JSON)</v>
+        <v>Request Body</v>
       </c>
       <c r="G1" t="str">
-        <v>Sample Response (JSON)</v>
+        <v>Sample Response</v>
       </c>
       <c r="H1" t="str">
-        <v>Success Status Code</v>
+        <v>Status Codes</v>
       </c>
       <c r="I1" t="str">
-        <v>Error Status Codes</v>
+        <v>Notes</v>
       </c>
     </row>
     <row r="2">
@@ -3823,13 +3914,13 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C2" t="str">
-        <v>GET</v>
+        <v>/api/hotel/profile</v>
       </c>
       <c r="D2" t="str">
-        <v>/api/hotel/profile</v>
+        <v>GET</v>
       </c>
       <c r="E2" t="str">
-        <v>Get hotel profile</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -3837,11 +3928,11 @@
       <c r="G2" t="str">
         <v>{ "user": {...}, "profile": {...} }</v>
       </c>
-      <c r="H2">
-        <v>200</v>
+      <c r="H2" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I2" t="str">
-        <v>401/403/500</v>
+        <v>Get hotel profile</v>
       </c>
     </row>
     <row r="3">
@@ -3852,28 +3943,25 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C3" t="str">
+        <v>/api/hotel/profile</v>
+      </c>
+      <c r="D3" t="str">
         <v>PUT</v>
       </c>
-      <c r="D3" t="str">
-        <v>/api/hotel/profile</v>
-      </c>
       <c r="E3" t="str">
+        <v>Bearer JWT (hotel_partner)</v>
+      </c>
+      <c r="F3" t="str">
+        <v>{ "hotelName": "Grand Palace", "email": "hotel@test.com", "phone": "7000000001", "address": "123 Main St", "city": "Jaipur", "starRating": 4 }</v>
+      </c>
+      <c r="G3" t="str">
+        <v>{ "message": "Profile updated" }</v>
+      </c>
+      <c r="H3" t="str">
+        <v>200 on success; 401/403/500 on error</v>
+      </c>
+      <c r="I3" t="str">
         <v>Update hotel profile</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>{ "hotelName": "Grand Palace", "email": "hotel@test.com", "phone": "7000000001", "address": "123 Main St", "city": "Jaipur", "starRating": 4 }</v>
-      </c>
-      <c r="H3" t="str">
-        <v>{ "message": "Profile updated" }</v>
-      </c>
-      <c r="I3">
-        <v>200</v>
-      </c>
-      <c r="J3" t="str">
-        <v>401/403/500</v>
       </c>
     </row>
     <row r="4">
@@ -3884,13 +3972,13 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C4" t="str">
-        <v>GET</v>
+        <v>/api/hotel/settings</v>
       </c>
       <c r="D4" t="str">
-        <v>/api/hotel/settings</v>
+        <v>GET</v>
       </c>
       <c r="E4" t="str">
-        <v>Get hotel settings</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -3898,11 +3986,11 @@
       <c r="G4" t="str">
         <v>{ "settings": {...} }</v>
       </c>
-      <c r="H4">
-        <v>200</v>
+      <c r="H4" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I4" t="str">
-        <v>401/403/500</v>
+        <v>Get hotel settings</v>
       </c>
     </row>
     <row r="5">
@@ -3913,28 +4001,25 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C5" t="str">
+        <v>/api/hotel/settings</v>
+      </c>
+      <c r="D5" t="str">
         <v>PUT</v>
       </c>
-      <c r="D5" t="str">
-        <v>/api/hotel/settings</v>
-      </c>
       <c r="E5" t="str">
+        <v>Bearer JWT (hotel_partner)</v>
+      </c>
+      <c r="F5" t="str">
+        <v>{ "emailNotifications": true }</v>
+      </c>
+      <c r="G5" t="str">
+        <v>{ "message": "Settings updated" }</v>
+      </c>
+      <c r="H5" t="str">
+        <v>200 on success; 401/403/500 on error</v>
+      </c>
+      <c r="I5" t="str">
         <v>Update hotel settings</v>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v>{ "emailNotifications": true }</v>
-      </c>
-      <c r="H5" t="str">
-        <v>{ "message": "Settings updated" }</v>
-      </c>
-      <c r="I5">
-        <v>200</v>
-      </c>
-      <c r="J5" t="str">
-        <v>401/403/500</v>
       </c>
     </row>
     <row r="6">
@@ -3945,13 +4030,13 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C6" t="str">
-        <v>GET</v>
+        <v>/api/hotel/rooms</v>
       </c>
       <c r="D6" t="str">
-        <v>/api/hotel/rooms</v>
+        <v>GET</v>
       </c>
       <c r="E6" t="str">
-        <v>List hotel rooms</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -3959,11 +4044,11 @@
       <c r="G6" t="str">
         <v>{ "rooms": [...] }</v>
       </c>
-      <c r="H6">
-        <v>200</v>
+      <c r="H6" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I6" t="str">
-        <v>401/403/500</v>
+        <v>List hotel rooms. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="7">
@@ -3974,13 +4059,13 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C7" t="str">
+        <v>/api/hotel/rooms</v>
+      </c>
+      <c r="D7" t="str">
         <v>POST</v>
       </c>
-      <c r="D7" t="str">
-        <v>/api/hotel/rooms</v>
-      </c>
       <c r="E7" t="str">
-        <v>Create hotel room</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F7" t="str">
         <v>{ "type": "Deluxe", "total": 10, "price": 3500 }</v>
@@ -3988,11 +4073,11 @@
       <c r="G7" t="str">
         <v>{ "message": "Room created" }</v>
       </c>
-      <c r="H7">
-        <v>201</v>
+      <c r="H7" t="str">
+        <v>201 on success; 401/403/400/500 on error</v>
       </c>
       <c r="I7" t="str">
-        <v>401/403/400/500</v>
+        <v>Create hotel room</v>
       </c>
     </row>
     <row r="8">
@@ -4003,28 +4088,25 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C8" t="str">
+        <v>/api/hotel/rooms/:id</v>
+      </c>
+      <c r="D8" t="str">
         <v>PUT</v>
       </c>
-      <c r="D8" t="str">
-        <v>/api/hotel/rooms/:id</v>
-      </c>
       <c r="E8" t="str">
-        <v>Update room</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F8" t="str">
-        <v>/{id}</v>
+        <v>{ "available": 3 }</v>
       </c>
       <c r="G8" t="str">
-        <v>{ "available": 3 }</v>
+        <v>{ "message": "Room updated" }</v>
       </c>
       <c r="H8" t="str">
-        <v>{ "message": "Room updated" }</v>
-      </c>
-      <c r="I8">
-        <v>200</v>
-      </c>
-      <c r="J8" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Update room. Path params: {id}</v>
       </c>
     </row>
     <row r="9">
@@ -4035,28 +4117,25 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C9" t="str">
+        <v>/api/hotel/rooms/:id</v>
+      </c>
+      <c r="D9" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D9" t="str">
-        <v>/api/hotel/rooms/:id</v>
-      </c>
       <c r="E9" t="str">
-        <v>Delete room</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F9" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>{ "message": "Room deleted" }</v>
       </c>
       <c r="H9" t="str">
-        <v>{ "message": "Room deleted" }</v>
-      </c>
-      <c r="I9">
-        <v>200</v>
-      </c>
-      <c r="J9" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Delete room. Path params: {id}</v>
       </c>
     </row>
     <row r="10">
@@ -4067,13 +4146,13 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C10" t="str">
-        <v>GET</v>
+        <v>/api/hotel/pricing</v>
       </c>
       <c r="D10" t="str">
-        <v>/api/hotel/pricing</v>
+        <v>GET</v>
       </c>
       <c r="E10" t="str">
-        <v>Get pricing</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -4081,11 +4160,11 @@
       <c r="G10" t="str">
         <v>{ "pricing": [...] }</v>
       </c>
-      <c r="H10">
-        <v>200</v>
+      <c r="H10" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I10" t="str">
-        <v>401/403/500</v>
+        <v>Get pricing. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="11">
@@ -4096,28 +4175,25 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C11" t="str">
+        <v>/api/hotel/pricing/:id</v>
+      </c>
+      <c r="D11" t="str">
         <v>PUT</v>
       </c>
-      <c r="D11" t="str">
-        <v>/api/hotel/pricing/:id</v>
-      </c>
       <c r="E11" t="str">
-        <v>Update pricing</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F11" t="str">
-        <v>/{id}</v>
+        <v>{ "price": 4000 }</v>
       </c>
       <c r="G11" t="str">
-        <v>{ "price": 4000 }</v>
+        <v>{ "message": "Pricing updated" }</v>
       </c>
       <c r="H11" t="str">
-        <v>{ "message": "Pricing updated" }</v>
-      </c>
-      <c r="I11">
-        <v>200</v>
-      </c>
-      <c r="J11" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Update pricing. Path params: {id}</v>
       </c>
     </row>
     <row r="12">
@@ -4128,13 +4204,13 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C12" t="str">
-        <v>GET</v>
+        <v>/api/hotel/availability</v>
       </c>
       <c r="D12" t="str">
-        <v>/api/hotel/availability</v>
+        <v>GET</v>
       </c>
       <c r="E12" t="str">
-        <v>Get availability</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -4142,11 +4218,11 @@
       <c r="G12" t="str">
         <v>{ "availability": [...] }</v>
       </c>
-      <c r="H12">
-        <v>200</v>
+      <c r="H12" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I12" t="str">
-        <v>401/403/500</v>
+        <v>Get availability. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="13">
@@ -4157,13 +4233,13 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C13" t="str">
+        <v>/api/hotel/availability/bulk</v>
+      </c>
+      <c r="D13" t="str">
         <v>PUT</v>
       </c>
-      <c r="D13" t="str">
-        <v>/api/hotel/availability/bulk</v>
-      </c>
       <c r="E13" t="str">
-        <v>Update availability (bulk)</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F13" t="str">
         <v>{ "date": "2026-12-25", "availability": [{ "roomType": "Deluxe", "available": 5 }] }</v>
@@ -4171,11 +4247,11 @@
       <c r="G13" t="str">
         <v>{ "message": "Availability updated" }</v>
       </c>
-      <c r="H13">
-        <v>200</v>
+      <c r="H13" t="str">
+        <v>200 on success; 401/403/400/500 on error</v>
       </c>
       <c r="I13" t="str">
-        <v>401/403/400/500</v>
+        <v>Update availability (bulk)</v>
       </c>
     </row>
     <row r="14">
@@ -4186,13 +4262,13 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C14" t="str">
-        <v>GET</v>
+        <v>/api/hotel/bookings</v>
       </c>
       <c r="D14" t="str">
-        <v>/api/hotel/bookings</v>
+        <v>GET</v>
       </c>
       <c r="E14" t="str">
-        <v>List bookings</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -4200,11 +4276,11 @@
       <c r="G14" t="str">
         <v>{ "bookings": [...] }</v>
       </c>
-      <c r="H14">
-        <v>200</v>
+      <c r="H14" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I14" t="str">
-        <v>401/403/500</v>
+        <v>List bookings. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="15">
@@ -4215,13 +4291,13 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C15" t="str">
+        <v>/api/hotel/bookings</v>
+      </c>
+      <c r="D15" t="str">
         <v>POST</v>
       </c>
-      <c r="D15" t="str">
-        <v>/api/hotel/bookings</v>
-      </c>
       <c r="E15" t="str">
-        <v>Create booking</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F15" t="str">
         <v>{ "guestName": "John", "checkInDate": "2026-12-25", "guests": 2, "amount": 12000 }</v>
@@ -4229,11 +4305,11 @@
       <c r="G15" t="str">
         <v>{ "message": "Booking created" }</v>
       </c>
-      <c r="H15">
-        <v>201</v>
+      <c r="H15" t="str">
+        <v>201 on success; 401/403/400/500 on error</v>
       </c>
       <c r="I15" t="str">
-        <v>401/403/400/500</v>
+        <v>Create booking</v>
       </c>
     </row>
     <row r="16">
@@ -4244,28 +4320,25 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C16" t="str">
+        <v>/api/hotel/bookings/:id</v>
+      </c>
+      <c r="D16" t="str">
         <v>PUT</v>
       </c>
-      <c r="D16" t="str">
-        <v>/api/hotel/bookings/:id</v>
-      </c>
       <c r="E16" t="str">
-        <v>Update booking</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F16" t="str">
-        <v>/{id}</v>
+        <v>{ "status": "confirmed" }</v>
       </c>
       <c r="G16" t="str">
-        <v>{ "status": "confirmed" }</v>
+        <v>{ "message": "Booking updated" }</v>
       </c>
       <c r="H16" t="str">
-        <v>{ "message": "Booking updated" }</v>
-      </c>
-      <c r="I16">
-        <v>200</v>
-      </c>
-      <c r="J16" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Update booking. Path params: {id}</v>
       </c>
     </row>
     <row r="17">
@@ -4276,28 +4349,25 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C17" t="str">
+        <v>/api/hotel/bookings/:id</v>
+      </c>
+      <c r="D17" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D17" t="str">
-        <v>/api/hotel/bookings/:id</v>
-      </c>
       <c r="E17" t="str">
-        <v>Delete booking</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F17" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>{ "message": "Booking deleted" }</v>
       </c>
       <c r="H17" t="str">
-        <v>{ "message": "Booking deleted" }</v>
-      </c>
-      <c r="I17">
-        <v>200</v>
-      </c>
-      <c r="J17" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Delete booking. Path params: {id}</v>
       </c>
     </row>
     <row r="18">
@@ -4308,28 +4378,25 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C18" t="str">
+        <v>/api/hotel/bookings/:id/pay</v>
+      </c>
+      <c r="D18" t="str">
         <v>PUT</v>
       </c>
-      <c r="D18" t="str">
-        <v>/api/hotel/bookings/:id/pay</v>
-      </c>
       <c r="E18" t="str">
-        <v>Process payment</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F18" t="str">
-        <v>/{id}</v>
+        <v>{ "paidAmount": 12000 }</v>
       </c>
       <c r="G18" t="str">
-        <v>{ "paidAmount": 12000 }</v>
+        <v>{ "message": "Payment recorded" }</v>
       </c>
       <c r="H18" t="str">
-        <v>{ "message": "Payment recorded" }</v>
-      </c>
-      <c r="I18">
-        <v>200</v>
-      </c>
-      <c r="J18" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Process payment. Path params: {id}</v>
       </c>
     </row>
     <row r="19">
@@ -4340,13 +4407,13 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C19" t="str">
-        <v>GET</v>
+        <v>/api/hotel/guests</v>
       </c>
       <c r="D19" t="str">
-        <v>/api/hotel/guests</v>
+        <v>GET</v>
       </c>
       <c r="E19" t="str">
-        <v>List guests</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -4354,11 +4421,11 @@
       <c r="G19" t="str">
         <v>{ "bookings": [...] }</v>
       </c>
-      <c r="H19">
-        <v>200</v>
+      <c r="H19" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I19" t="str">
-        <v>401/403/500</v>
+        <v>List guests. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="20">
@@ -4369,13 +4436,13 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C20" t="str">
-        <v>GET</v>
+        <v>/api/hotel/reviews</v>
       </c>
       <c r="D20" t="str">
-        <v>/api/hotel/reviews</v>
+        <v>GET</v>
       </c>
       <c r="E20" t="str">
-        <v>List reviews</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -4383,11 +4450,11 @@
       <c r="G20" t="str">
         <v>{ "reviews": [...] }</v>
       </c>
-      <c r="H20">
-        <v>200</v>
+      <c r="H20" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I20" t="str">
-        <v>401/403/500</v>
+        <v>List reviews. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="21">
@@ -4398,28 +4465,25 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C21" t="str">
+        <v>/api/hotel/reviews/:id/respond</v>
+      </c>
+      <c r="D21" t="str">
         <v>PUT</v>
       </c>
-      <c r="D21" t="str">
-        <v>/api/hotel/reviews/:id/respond</v>
-      </c>
       <c r="E21" t="str">
-        <v>Respond to review</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F21" t="str">
-        <v>/{id}</v>
+        <v>{ "response": "Thank you!" }</v>
       </c>
       <c r="G21" t="str">
-        <v>{ "response": "Thank you!" }</v>
+        <v>{ "message": "Review responded" }</v>
       </c>
       <c r="H21" t="str">
-        <v>{ "message": "Review responded" }</v>
-      </c>
-      <c r="I21">
-        <v>200</v>
-      </c>
-      <c r="J21" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Respond to review. Path params: {id}</v>
       </c>
     </row>
     <row r="22">
@@ -4430,28 +4494,25 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C22" t="str">
+        <v>/api/hotel/reviews/:id/status</v>
+      </c>
+      <c r="D22" t="str">
         <v>PUT</v>
       </c>
-      <c r="D22" t="str">
-        <v>/api/hotel/reviews/:id/status</v>
-      </c>
       <c r="E22" t="str">
-        <v>Update review status</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F22" t="str">
-        <v>/{id}</v>
+        <v>{ "status": "approved" }</v>
       </c>
       <c r="G22" t="str">
-        <v>{ "status": "approved" }</v>
+        <v>{ "message": "Status updated" }</v>
       </c>
       <c r="H22" t="str">
-        <v>{ "message": "Status updated" }</v>
-      </c>
-      <c r="I22">
-        <v>200</v>
-      </c>
-      <c r="J22" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Update review status. Path params: {id}</v>
       </c>
     </row>
     <row r="23">
@@ -4462,28 +4523,25 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C23" t="str">
+        <v>/api/hotel/reviews/:id</v>
+      </c>
+      <c r="D23" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D23" t="str">
-        <v>/api/hotel/reviews/:id</v>
-      </c>
       <c r="E23" t="str">
-        <v>Delete review</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F23" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>{ "message": "Review deleted" }</v>
       </c>
       <c r="H23" t="str">
-        <v>{ "message": "Review deleted" }</v>
-      </c>
-      <c r="I23">
-        <v>200</v>
-      </c>
-      <c r="J23" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Delete review. Path params: {id}</v>
       </c>
     </row>
     <row r="24">
@@ -4494,13 +4552,13 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C24" t="str">
-        <v>GET</v>
+        <v>/api/hotel/revenue</v>
       </c>
       <c r="D24" t="str">
-        <v>/api/hotel/revenue</v>
+        <v>GET</v>
       </c>
       <c r="E24" t="str">
-        <v>Get revenue</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -4508,11 +4566,11 @@
       <c r="G24" t="str">
         <v>{ "totalRevenue": 500000 }</v>
       </c>
-      <c r="H24">
-        <v>200</v>
+      <c r="H24" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I24" t="str">
-        <v>401/403/500</v>
+        <v>Get revenue</v>
       </c>
     </row>
     <row r="25">
@@ -4523,13 +4581,13 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C25" t="str">
-        <v>GET</v>
+        <v>/api/hotel/notifications</v>
       </c>
       <c r="D25" t="str">
-        <v>/api/hotel/notifications</v>
+        <v>GET</v>
       </c>
       <c r="E25" t="str">
-        <v>List notifications</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -4537,11 +4595,11 @@
       <c r="G25" t="str">
         <v>{ "notifications": [...] }</v>
       </c>
-      <c r="H25">
-        <v>200</v>
+      <c r="H25" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I25" t="str">
-        <v>401/403/500</v>
+        <v>List notifications. Supports ?page &amp; ?limit (?limit=all returns every row); response adds a "pagination" object</v>
       </c>
     </row>
     <row r="26">
@@ -4552,13 +4610,13 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C26" t="str">
+        <v>/api/hotel/notifications/read-all</v>
+      </c>
+      <c r="D26" t="str">
         <v>PUT</v>
       </c>
-      <c r="D26" t="str">
-        <v>/api/hotel/notifications/read-all</v>
-      </c>
       <c r="E26" t="str">
-        <v>Mark all read</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -4566,11 +4624,11 @@
       <c r="G26" t="str">
         <v>{ "message": "All marked as read" }</v>
       </c>
-      <c r="H26">
-        <v>200</v>
+      <c r="H26" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I26" t="str">
-        <v>401/403/500</v>
+        <v>Mark all read</v>
       </c>
     </row>
     <row r="27">
@@ -4581,28 +4639,25 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C27" t="str">
+        <v>/api/hotel/notifications/:id/read</v>
+      </c>
+      <c r="D27" t="str">
         <v>PUT</v>
       </c>
-      <c r="D27" t="str">
-        <v>/api/hotel/notifications/:id/read</v>
-      </c>
       <c r="E27" t="str">
-        <v>Mark notification read</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F27" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>{ "message": "Notification marked as read" }</v>
       </c>
       <c r="H27" t="str">
-        <v>{ "message": "Notification marked as read" }</v>
-      </c>
-      <c r="I27">
-        <v>200</v>
-      </c>
-      <c r="J27" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Mark notification read. Path params: {id}</v>
       </c>
     </row>
     <row r="28">
@@ -4613,28 +4668,25 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C28" t="str">
+        <v>/api/hotel/notifications/:id</v>
+      </c>
+      <c r="D28" t="str">
         <v>DELETE</v>
       </c>
-      <c r="D28" t="str">
-        <v>/api/hotel/notifications/:id</v>
-      </c>
       <c r="E28" t="str">
-        <v>Delete notification</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F28" t="str">
-        <v>/{id}</v>
+        <v/>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>{ "message": "Notification deleted" }</v>
       </c>
       <c r="H28" t="str">
-        <v>{ "message": "Notification deleted" }</v>
-      </c>
-      <c r="I28">
-        <v>200</v>
-      </c>
-      <c r="J28" t="str">
-        <v>404/401/403/500</v>
+        <v>200 on success; 404/401/403/500 on error</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Delete notification. Path params: {id}</v>
       </c>
     </row>
     <row r="29">
@@ -4645,13 +4697,13 @@
         <v>Hotel Partner</v>
       </c>
       <c r="C29" t="str">
-        <v>GET</v>
+        <v>/api/hotel/analytics</v>
       </c>
       <c r="D29" t="str">
-        <v>/api/hotel/analytics</v>
+        <v>GET</v>
       </c>
       <c r="E29" t="str">
-        <v>Get hotel analytics</v>
+        <v>Bearer JWT (hotel_partner)</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -4659,16 +4711,17 @@
       <c r="G29" t="str">
         <v>{ "stats": {...} }</v>
       </c>
-      <c r="H29">
-        <v>200</v>
+      <c r="H29" t="str">
+        <v>200 on success; 401/403/500 on error</v>
       </c>
       <c r="I29" t="str">
-        <v>401/403/500</v>
+        <v>Get hotel analytics</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I29"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I29"/>
   </ignoredErrors>
 </worksheet>
 </file>